--- a/error_models/conv_models/nv_16x16_b1_dat-524288_wt-65536_int8/unique_complete_df.xlsx
+++ b/error_models/conv_models/nv_16x16_b1_dat-524288_wt-65536_int8/unique_complete_df.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T40"/>
+  <dimension ref="A1:AT40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,6 +529,136 @@
           <t>Skip4</t>
         </is>
       </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>same_row-single</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>same_row-multi</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>single_block-single</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>single_block-multi</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>quasi_shattered_channel-single</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>quasi_shattered_channel-multi</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>bullet_wake-single</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>bullet_wake-multi</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>skip_4-single</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>skip_4-multi</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>single_channel_alternated_blocks-single</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>single_channel_alternated_blocks-multi</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>multi_channel_block-single</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>multi_channel_block-multi</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>full_channels-single</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>full_channels-multi</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>single-single</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>single-multi</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>shattered_channel-single</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>shattered_channel-multi</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>single_channel_random-single</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>single_channel_random-multi</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>multiple_channels_uncategorized-single</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>multiple_channels_uncategorized-multi</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>rectangles-single</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>rectangles-multi</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -552,13 +682,13 @@
         <v>2</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9869679151661106</v>
+        <v>0.989938067577842</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0130202231046931</v>
+        <v>0.0100524652125198</v>
       </c>
       <c r="I2" t="n">
-        <v>1.178978506546804e-05</v>
+        <v>9.395265507342336e-06</v>
       </c>
       <c r="J2" t="n">
         <v>0.8301031552357492</v>
@@ -592,6 +722,84 @@
       </c>
       <c r="T2" t="n">
         <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>0.1123068442346615</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>0.8876931557653385</v>
       </c>
     </row>
     <row r="3">
@@ -616,16 +824,16 @@
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9928570823981578</v>
+        <v>0.9936335735313528</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0071297822067981</v>
+        <v>0.0063555372189197</v>
       </c>
       <c r="I3" t="n">
-        <v>1.30634509134087e-05</v>
+        <v>1.081730559679619e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6655232138490073</v>
+        <v>0.6655232138490071</v>
       </c>
       <c r="K3" t="n">
         <v>0.1746988191661234</v>
@@ -643,7 +851,7 @@
         <v>0.0156080459740758</v>
       </c>
       <c r="P3" t="n">
-        <v>4.090382600848705e-06</v>
+        <v>4.090382600848706e-06</v>
       </c>
       <c r="Q3" t="n">
         <v>0.005260536858786</v>
@@ -656,6 +864,84 @@
       </c>
       <c r="T3" t="n">
         <v>0.0001537184775482</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>0.1123065974034061</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>0.8876934025965939</v>
       </c>
     </row>
     <row r="4">
@@ -680,16 +966,16 @@
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>0.997865771754901</v>
+        <v>0.998041028300635</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0021200999087948</v>
+        <v>0.001946591312892</v>
       </c>
       <c r="I4" t="n">
-        <v>1.405639217344054e-05</v>
+        <v>1.230844234213843e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1376520177535576</v>
+        <v>0.1376520177535577</v>
       </c>
       <c r="K4" t="n">
         <v>0.6997218227144739</v>
@@ -720,6 +1006,84 @@
       </c>
       <c r="T4" t="n">
         <v>0.0002929536633534</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.9989303491014304</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.0010696508985694</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>0.1123077430083088</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0.8876922569916912</v>
       </c>
     </row>
     <row r="5">
@@ -744,19 +1108,19 @@
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9957864436240992</v>
+        <v>0.9960600443366232</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0041998757511318</v>
+        <v>0.0039280264296344</v>
       </c>
       <c r="I5" t="n">
-        <v>1.360868063825878e-05</v>
+        <v>1.185728961150844e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2968514870191589</v>
+        <v>0.296851487019159</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5369724086304438</v>
+        <v>0.5369724086304439</v>
       </c>
       <c r="L5" t="n">
         <v>0.0673676715119646</v>
@@ -784,6 +1148,84 @@
       </c>
       <c r="T5" t="n">
         <v>0.0008829264762429</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.998929282587338</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.0010707174126619</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0.1123161279701659</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0.887683872029834</v>
       </c>
     </row>
     <row r="6">
@@ -808,19 +1250,19 @@
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9964511105147292</v>
+        <v>0.9967934665800861</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0035347930122003</v>
+        <v>0.003194237520413</v>
       </c>
       <c r="I6" t="n">
-        <v>1.402452893968527e-05</v>
+        <v>1.222395537010034e-05</v>
       </c>
       <c r="J6" t="n">
         <v>0.3453130986944279</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4984717530323769</v>
+        <v>0.4984717530323768</v>
       </c>
       <c r="L6" t="n">
         <v>0.0494725525552405</v>
@@ -838,7 +1280,7 @@
         <v>1.003086683818171e-06</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.055683639850124e-05</v>
+        <v>1.055683639850125e-05</v>
       </c>
       <c r="R6" t="n">
         <v>0.0032680915135873</v>
@@ -848,6 +1290,84 @@
       </c>
       <c r="T6" t="n">
         <v>0.000707915894692</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.9981805648057058</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.0018194351942942</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0.1123161067701795</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0.8876838932298206</v>
       </c>
     </row>
     <row r="7">
@@ -872,13 +1392,13 @@
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9799100445144674</v>
+        <v>0.9861272350558278</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0200762941960186</v>
+        <v>0.0138613526319897</v>
       </c>
       <c r="I7" t="n">
-        <v>1.358934538326772e-05</v>
+        <v>1.134036805168828e-05</v>
       </c>
       <c r="J7" t="n">
         <v>0.8300939230624722</v>
@@ -887,7 +1407,7 @@
         <v>0.0237932077100839</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0340772367786083</v>
+        <v>0.0340772367786082</v>
       </c>
       <c r="M7" t="n">
         <v>1.100436527133691e-05</v>
@@ -912,6 +1432,84 @@
       </c>
       <c r="T7" t="n">
         <v>1.13693161209331e-06</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0.1123071268636662</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0.8876928731363338</v>
       </c>
     </row>
     <row r="8">
@@ -936,13 +1534,13 @@
         <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9932506583711478</v>
+        <v>0.9950562533293884</v>
       </c>
       <c r="H8" t="n">
-        <v>0.006736111457238</v>
+        <v>0.0049326674122344</v>
       </c>
       <c r="I8" t="n">
-        <v>1.315822748337043e-05</v>
+        <v>1.100731424655236e-05</v>
       </c>
       <c r="J8" t="n">
         <v>0.8123051446570934</v>
@@ -976,6 +1574,84 @@
       </c>
       <c r="T8" t="n">
         <v>0.0033326246736416</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0.1123072296378497</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0.8876927703621503</v>
       </c>
     </row>
     <row r="9">
@@ -1000,13 +1676,13 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9955451872279816</v>
+        <v>0.9979818033372152</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0044394256508886</v>
+        <v>0.0020046124804475</v>
       </c>
       <c r="I9" t="n">
-        <v>1.531517699893181e-05</v>
+        <v>1.351223820642841e-05</v>
       </c>
       <c r="J9" t="n">
         <v>0.8133054747516359</v>
@@ -1040,6 +1716,84 @@
       </c>
       <c r="T9" t="n">
         <v>1.201050778277717e-07</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1064,19 +1818,19 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.999158004664626</v>
+        <v>0.9992123452401048</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0008284536193368</v>
+        <v>0.00077555111694</v>
       </c>
       <c r="I10" t="n">
-        <v>1.346977190645851e-05</v>
+        <v>1.203169882427591e-05</v>
       </c>
       <c r="J10" t="n">
         <v>0.0034157852262598</v>
       </c>
       <c r="K10" t="n">
-        <v>0.8909289871033366</v>
+        <v>0.8909289871033365</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1103,6 +1857,84 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1128,13 +1960,13 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9997152840023744</v>
+        <v>0.9997790829556183</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0002704286545742</v>
+        <v>0.0002083405365856</v>
       </c>
       <c r="I11" t="n">
-        <v>1.421539892057017e-05</v>
+        <v>1.250456366512909e-05</v>
       </c>
       <c r="J11" t="n">
         <v>0.0014613408283693</v>
@@ -1149,7 +1981,7 @@
         <v>0.0004430480130373</v>
       </c>
       <c r="N11" t="n">
-        <v>6.832494497582257e-06</v>
+        <v>6.832494497582256e-06</v>
       </c>
       <c r="O11" t="n">
         <v>5.949476414616127e-08</v>
@@ -1167,6 +1999,84 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1192,13 +2102,13 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9977677983628152</v>
+        <v>0.998633020725647</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0022174112105151</v>
+        <v>0.0013537488929388</v>
       </c>
       <c r="I12" t="n">
-        <v>1.471848253880223e-05</v>
+        <v>1.315843728348307e-05</v>
       </c>
       <c r="J12" t="n">
         <v>0.45633503951514</v>
@@ -1232,6 +2142,84 @@
       </c>
       <c r="T12" t="n">
         <v>2.300551734483913e-06</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1256,16 +2244,16 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0.9981887419608684</v>
+        <v>0.9992513280379915</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0017964383253432</v>
+        <v>0.0007357537838654</v>
       </c>
       <c r="I13" t="n">
-        <v>1.474776965745262e-05</v>
+        <v>1.28462340120047e-05</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5653425193494622</v>
+        <v>0.5653425193494623</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1296,6 +2284,84 @@
       </c>
       <c r="T13" t="n">
         <v>7.241464673763863e-08</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1320,13 +2386,13 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0.9973606919928636</v>
+        <v>0.9980101902429822</v>
       </c>
       <c r="H14" t="n">
-        <v>0.002624832384611</v>
+        <v>0.0019768368364713</v>
       </c>
       <c r="I14" t="n">
-        <v>1.440367839464569e-05</v>
+        <v>1.290097641579972e-05</v>
       </c>
       <c r="J14" t="n">
         <v>0.259768404538699</v>
@@ -1360,6 +2426,84 @@
       </c>
       <c r="T14" t="n">
         <v>1.625198384158754e-06</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1384,13 +2528,13 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9990369540592464</v>
+        <v>0.9995871251755344</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0009482526645265</v>
+        <v>0.0003999668504629</v>
       </c>
       <c r="I15" t="n">
-        <v>1.472133209629254e-05</v>
+        <v>1.283602987200232e-05</v>
       </c>
       <c r="J15" t="n">
         <v>0.2683870752884121</v>
@@ -1423,6 +2567,84 @@
         <v>0.0126379876210933</v>
       </c>
       <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1448,13 +2670,13 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9996943045167324</v>
+        <v>0.999823703362223</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0002919998047758</v>
+        <v>0.000164662249148</v>
       </c>
       <c r="I16" t="n">
-        <v>1.362373436116212e-05</v>
+        <v>1.156244449812495e-05</v>
       </c>
       <c r="J16" t="n">
         <v>0.0002036607974802</v>
@@ -1475,7 +2697,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9244544404151052</v>
+        <v>0.9244544404151054</v>
       </c>
       <c r="Q16" t="n">
         <v>0.0603999406241808</v>
@@ -1487,6 +2709,84 @@
         <v>0.0148857561507216</v>
       </c>
       <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1512,13 +2812,13 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9987154813245234</v>
+        <v>0.9989937428205226</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0012705805399389</v>
+        <v>0.0009938038433056</v>
       </c>
       <c r="I17" t="n">
-        <v>1.386619140681473e-05</v>
+        <v>1.238139204092512e-05</v>
       </c>
       <c r="J17" t="n">
         <v>0.1185343048526066</v>
@@ -1539,7 +2839,7 @@
         <v>8.409054246782047e-09</v>
       </c>
       <c r="P17" t="n">
-        <v>0.7209284435398772</v>
+        <v>0.7209284435398771</v>
       </c>
       <c r="Q17" t="n">
         <v>0.1425297993636328</v>
@@ -1552,6 +2852,84 @@
       </c>
       <c r="T17" t="n">
         <v>0.0007252121557806</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1576,13 +2954,13 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9995575805104372</v>
+        <v>0.9997876940183806</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0004284131589334</v>
+        <v>0.0002003691030704</v>
       </c>
       <c r="I18" t="n">
-        <v>1.393438649857142e-05</v>
+        <v>1.186493441820197e-05</v>
       </c>
       <c r="J18" t="n">
         <v>0.08317730312664109</v>
@@ -1616,6 +2994,84 @@
       </c>
       <c r="T18" t="n">
         <v>3.071643734142219e-07</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1640,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.9993073670916254</v>
+        <v>0.9994269673805618</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0006785807617539</v>
+        <v>0.0005605480318403001</v>
       </c>
       <c r="I19" t="n">
-        <v>1.398020248983604e-05</v>
+        <v>1.241264346720166e-05</v>
       </c>
       <c r="J19" t="n">
         <v>0.0556772342928949</v>
@@ -1679,6 +3135,84 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1704,13 +3238,13 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.999780246084066</v>
+        <v>0.9998428001068322</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0002060340881617</v>
+        <v>0.0001453265810242</v>
       </c>
       <c r="I20" t="n">
-        <v>1.364788364130725e-05</v>
+        <v>1.180136801295648e-05</v>
       </c>
       <c r="J20" t="n">
         <v>0.0001750162828316</v>
@@ -1743,6 +3277,84 @@
         <v>0</v>
       </c>
       <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1768,19 +3380,19 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.9990287909621266</v>
+        <v>0.9990872820628892</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0009571995482649</v>
+        <v>0.0009001459986948</v>
       </c>
       <c r="I21" t="n">
-        <v>1.39375454777084e-05</v>
+        <v>1.249999428529224e-05</v>
       </c>
       <c r="J21" t="n">
         <v>0.0176177432633315</v>
       </c>
       <c r="K21" t="n">
-        <v>0.8760743736687527</v>
+        <v>0.8760743736687528</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -1789,10 +3401,10 @@
         <v>0.0032392287281422</v>
       </c>
       <c r="N21" t="n">
-        <v>9.830337200406026e-06</v>
+        <v>9.830337200406028e-06</v>
       </c>
       <c r="O21" t="n">
-        <v>2.517766164321583e-07</v>
+        <v>2.517766164321582e-07</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
@@ -1807,6 +3419,84 @@
         <v>0</v>
       </c>
       <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1832,19 +3522,19 @@
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0929769551569381</v>
+        <v>0.6047956804734581</v>
       </c>
       <c r="H22" t="n">
-        <v>0.9070088246301162</v>
+        <v>0.3951914885139226</v>
       </c>
       <c r="I22" t="n">
-        <v>1.414826881494622e-05</v>
+        <v>1.275906848857813e-05</v>
       </c>
       <c r="J22" t="n">
         <v>0.0019859783867124</v>
       </c>
       <c r="K22" t="n">
-        <v>0.9926079576824413</v>
+        <v>0.992607957682441</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -1871,6 +3561,84 @@
         <v>0</v>
       </c>
       <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1896,19 +3664,19 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0974059950198851</v>
+        <v>0.6074735110475075</v>
       </c>
       <c r="H23" t="n">
-        <v>0.9025797043319328</v>
+        <v>0.3925135112501448</v>
       </c>
       <c r="I23" t="n">
-        <v>1.422870405137719e-05</v>
+        <v>1.290575821694673e-05</v>
       </c>
       <c r="J23" t="n">
         <v>0.0003133538067673</v>
       </c>
       <c r="K23" t="n">
-        <v>0.9973578015648834</v>
+        <v>0.9973578015648836</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -1935,6 +3703,84 @@
         <v>2.407772307816696e-07</v>
       </c>
       <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1960,13 +3806,13 @@
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0.9963368022358142</v>
+        <v>0.9970695128877189</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0036485436557411</v>
+        <v>0.0029172279509224</v>
       </c>
       <c r="I24" t="n">
-        <v>1.458216431381134e-05</v>
+        <v>1.318721722789544e-05</v>
       </c>
       <c r="J24" t="n">
         <v>0.3107657370665476</v>
@@ -1981,16 +3827,16 @@
         <v>0.0137826400945601</v>
       </c>
       <c r="N24" t="n">
-        <v>4.13150111968898e-06</v>
+        <v>4.131501119688981e-06</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>0.5193382262611818</v>
+        <v>0.5193382262611816</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.1509447336166755</v>
+        <v>0.1509447336166756</v>
       </c>
       <c r="R24" t="n">
         <v>7.684893760993781e-06</v>
@@ -2000,6 +3846,84 @@
       </c>
       <c r="T24" t="n">
         <v>1.281762046655575e-06</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -2024,13 +3948,13 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0.9974574753421001</v>
+        <v>0.9977361899898384</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0025284809088387</v>
+        <v>0.002251180065048</v>
       </c>
       <c r="I25" t="n">
-        <v>1.397180493026233e-05</v>
+        <v>1.255800098287789e-05</v>
       </c>
       <c r="J25" t="n">
         <v>0.1062440873159112</v>
@@ -2064,6 +3988,84 @@
       </c>
       <c r="T25" t="n">
         <v>0.0007705550521501</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -2088,13 +4090,13 @@
         <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>0.997576937268808</v>
+        <v>0.9978996468957716</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0024091345475181</v>
+        <v>0.002088054393033</v>
       </c>
       <c r="I26" t="n">
-        <v>1.38562395431554e-05</v>
+        <v>1.222676706468325e-05</v>
       </c>
       <c r="J26" t="n">
         <v>0.2974600457580698</v>
@@ -2115,7 +4117,7 @@
         <v>0.0612954103802613</v>
       </c>
       <c r="P26" t="n">
-        <v>0.5404976629843035</v>
+        <v>0.5404976629843032</v>
       </c>
       <c r="Q26" t="n">
         <v>2.178973390692558e-05</v>
@@ -2128,6 +4130,84 @@
       </c>
       <c r="T26" t="n">
         <v>0.0035543475003304</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>0.99891291148384</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.00108708851616</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>0.1123071720730748</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>0.8876928279269252</v>
       </c>
     </row>
     <row r="27">
@@ -2152,16 +4232,16 @@
         <v>1</v>
       </c>
       <c r="G27" t="n">
-        <v>0.9924467295475056</v>
+        <v>0.9939681638803052</v>
       </c>
       <c r="H27" t="n">
-        <v>0.0075401651936794</v>
+        <v>0.0060208876976284</v>
       </c>
       <c r="I27" t="n">
-        <v>1.303331468419302e-05</v>
+        <v>1.087647793571727e-05</v>
       </c>
       <c r="J27" t="n">
-        <v>0.8111874862260696</v>
+        <v>0.8111874862260695</v>
       </c>
       <c r="K27" t="n">
         <v>0.0295781053661147</v>
@@ -2192,6 +4272,84 @@
       </c>
       <c r="T27" t="n">
         <v>0.0001323598480781</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>0.9985468078339056</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.0014531921660943</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>0.112306893237816</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>0.887693106762184</v>
       </c>
     </row>
     <row r="28">
@@ -2216,13 +4374,13 @@
         <v>1</v>
       </c>
       <c r="G28" t="n">
-        <v>0.9968056720879582</v>
+        <v>0.9973987910946808</v>
       </c>
       <c r="H28" t="n">
-        <v>0.0031810196582348</v>
+        <v>0.0025898513951351</v>
       </c>
       <c r="I28" t="n">
-        <v>1.323630967611622e-05</v>
+        <v>1.128556605328127e-05</v>
       </c>
       <c r="J28" t="n">
         <v>0.5175300796328922</v>
@@ -2243,7 +4401,7 @@
         <v>0.0448569048099401</v>
       </c>
       <c r="P28" t="n">
-        <v>0.3131683820759408</v>
+        <v>0.3131683820759409</v>
       </c>
       <c r="Q28" t="n">
         <v>3.652281179583968e-05</v>
@@ -2256,6 +4414,84 @@
       </c>
       <c r="T28" t="n">
         <v>0.0006818120274181</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>0.9989476799554322</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.0010523200445677</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2280,13 +4516,13 @@
         <v>1</v>
       </c>
       <c r="G29" t="n">
-        <v>0.9937383588547524</v>
+        <v>0.9939839894714136</v>
       </c>
       <c r="H29" t="n">
-        <v>0.006248286032051</v>
+        <v>0.006004606648117</v>
       </c>
       <c r="I29" t="n">
-        <v>1.328316906595683e-05</v>
+        <v>1.133193633875389e-05</v>
       </c>
       <c r="J29" t="n">
         <v>0.2440916410489265</v>
@@ -2307,7 +4543,7 @@
         <v>0.0171460320715026</v>
       </c>
       <c r="P29" t="n">
-        <v>0.5885471278510411</v>
+        <v>0.588547127851041</v>
       </c>
       <c r="Q29" t="n">
         <v>0.0017351460934031</v>
@@ -2320,6 +4556,84 @@
       </c>
       <c r="T29" t="n">
         <v>0.0027379788624883</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>0.1123121919592639</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.8876878080407361</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>0.0015428068801426</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>0.9984571931198574</v>
       </c>
     </row>
     <row r="30">
@@ -2344,13 +4658,13 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0.09160589239601161</v>
+        <v>0.6039185723050603</v>
       </c>
       <c r="H30" t="n">
-        <v>0.908379987434069</v>
+        <v>0.3960686523785934</v>
       </c>
       <c r="I30" t="n">
-        <v>1.404822578872373e-05</v>
+        <v>1.270337221528492e-05</v>
       </c>
       <c r="J30" t="n">
         <v>0.0024219406271633</v>
@@ -2383,6 +4697,84 @@
         <v>6.63259340144458e-10</v>
       </c>
       <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2408,16 +4800,16 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0.9909437504870766</v>
+        <v>0.9942372319630149</v>
       </c>
       <c r="H31" t="n">
-        <v>0.0090411189924707</v>
+        <v>0.0057490723242243</v>
       </c>
       <c r="I31" t="n">
-        <v>1.505857632200734e-05</v>
+        <v>1.362376862989176e-05</v>
       </c>
       <c r="J31" t="n">
-        <v>0.2913398649250132</v>
+        <v>0.2913398649250131</v>
       </c>
       <c r="K31" t="n">
         <v>0.1845339298320646</v>
@@ -2435,7 +4827,7 @@
         <v>0.4066993251370034</v>
       </c>
       <c r="P31" t="n">
-        <v>4.750464348188708e-06</v>
+        <v>4.750464348188707e-06</v>
       </c>
       <c r="Q31" t="n">
         <v>0.1087555818306137</v>
@@ -2448,6 +4840,84 @@
       </c>
       <c r="T31" t="n">
         <v>7.165655153882498e-06</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2472,13 +4942,13 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0.985067227784854</v>
+        <v>0.9878337608721716</v>
       </c>
       <c r="H32" t="n">
-        <v>0.0149185551475007</v>
+        <v>0.0121534044896834</v>
       </c>
       <c r="I32" t="n">
-        <v>1.414512351441126e-05</v>
+        <v>1.276269401423186e-05</v>
       </c>
       <c r="J32" t="n">
         <v>0.196607632267833</v>
@@ -2493,13 +4963,13 @@
         <v>0.005860723072928</v>
       </c>
       <c r="N32" t="n">
-        <v>7.199600275114014e-06</v>
+        <v>7.199600275114015e-06</v>
       </c>
       <c r="O32" t="n">
         <v>2.862300600227678e-06</v>
       </c>
       <c r="P32" t="n">
-        <v>5.26745274253618e-06</v>
+        <v>5.267452742536179e-06</v>
       </c>
       <c r="Q32" t="n">
         <v>0.1403606181919595</v>
@@ -2512,6 +4982,84 @@
       </c>
       <c r="T32" t="n">
         <v>3.496512662296734e-06</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2536,13 +5084,13 @@
         <v>2</v>
       </c>
       <c r="G33" t="n">
-        <v>0.9807167513973885</v>
+        <v>0.9822800990318052</v>
       </c>
       <c r="H33" t="n">
-        <v>0.0192712138762745</v>
+        <v>0.0177102005067201</v>
       </c>
       <c r="I33" t="n">
-        <v>1.196278220607099e-05</v>
+        <v>9.628517343854861e-06</v>
       </c>
       <c r="J33" t="n">
         <v>0.4582112183472372</v>
@@ -2576,6 +5124,84 @@
       </c>
       <c r="T33" t="n">
         <v>0.0111646141471378</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>0.9992452019200718</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>0.000754798079928</v>
       </c>
     </row>
     <row r="34">
@@ -2600,13 +5226,13 @@
         <v>2</v>
       </c>
       <c r="G34" t="n">
-        <v>0.1459767355781682</v>
+        <v>0.4281463068562242</v>
       </c>
       <c r="H34" t="n">
-        <v>0.8540105800738416</v>
+        <v>0.5718432752913393</v>
       </c>
       <c r="I34" t="n">
-        <v>1.261240385940752e-05</v>
+        <v>1.03459083057856e-05</v>
       </c>
       <c r="J34" t="n">
         <v>6.095147806080043e-05</v>
@@ -2640,6 +5266,84 @@
       </c>
       <c r="T34" t="n">
         <v>2.263592373948528e-05</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2664,13 +5368,13 @@
         <v>1</v>
       </c>
       <c r="G35" t="n">
-        <v>0.9794477852507228</v>
+        <v>0.9861063583764418</v>
       </c>
       <c r="H35" t="n">
-        <v>0.0205389761801035</v>
+        <v>0.013882674435053</v>
       </c>
       <c r="I35" t="n">
-        <v>1.316662504294414e-05</v>
+        <v>1.089524437443442e-05</v>
       </c>
       <c r="J35" t="n">
         <v>0.8300987708800671</v>
@@ -2704,6 +5408,84 @@
       </c>
       <c r="T35" t="n">
         <v>1.08069422628317e-06</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>0.1123069957607013</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>0.8876930042392988</v>
       </c>
     </row>
     <row r="36">
@@ -2728,13 +5510,13 @@
         <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>0.9669531034179868</v>
+        <v>0.9730003788124798</v>
       </c>
       <c r="H36" t="n">
-        <v>0.0330340989317856</v>
+        <v>0.0269890022343282</v>
       </c>
       <c r="I36" t="n">
-        <v>1.272570609695946e-05</v>
+        <v>1.054700906135771e-05</v>
       </c>
       <c r="J36" t="n">
         <v>0.7870533063295524</v>
@@ -2768,6 +5550,84 @@
       </c>
       <c r="T36" t="n">
         <v>0.0001911750509136396</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>0.0015410214832947</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>0.9984589785167053</v>
       </c>
     </row>
     <row r="37">
@@ -2792,13 +5652,13 @@
         <v>1</v>
       </c>
       <c r="G37" t="n">
-        <v>0.9887952409552909</v>
+        <v>0.9899345357179963</v>
       </c>
       <c r="H37" t="n">
-        <v>0.0111912307718815</v>
+        <v>0.0100540139827661</v>
       </c>
       <c r="I37" t="n">
-        <v>1.345632869668285e-05</v>
+        <v>1.137835510691081e-05</v>
       </c>
       <c r="J37" t="n">
         <v>0.4836089060462826</v>
@@ -2832,6 +5692,84 @@
       </c>
       <c r="T37" t="n">
         <v>0.0008213246420152983</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2856,13 +5794,13 @@
         <v>1</v>
       </c>
       <c r="G38" t="n">
-        <v>0.9918064209533994</v>
+        <v>0.9920292527745151</v>
       </c>
       <c r="H38" t="n">
-        <v>0.0081798896563111</v>
+        <v>0.007958957899431849</v>
       </c>
       <c r="I38" t="n">
-        <v>1.361744615870961e-05</v>
+        <v>1.171738192218124e-05</v>
       </c>
       <c r="J38" t="n">
         <v>0.1321941105946546</v>
@@ -2871,7 +5809,7 @@
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>0.07821215461237441</v>
+        <v>0.07821215461237445</v>
       </c>
       <c r="M38" t="n">
         <v>0.0166707717339195</v>
@@ -2896,6 +5834,84 @@
       </c>
       <c r="T38" t="n">
         <v>0.004936782684353699</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>0.1111022108638113</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.8888977891361887</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2920,13 +5936,13 @@
         <v>1</v>
       </c>
       <c r="G39" t="n">
-        <v>0.99381878235851</v>
+        <v>0.9940755102562981</v>
       </c>
       <c r="H39" t="n">
-        <v>0.006167641777525075</v>
+        <v>0.00591252417566685</v>
       </c>
       <c r="I39" t="n">
-        <v>1.350391983410717e-05</v>
+        <v>1.189362390425967e-05</v>
       </c>
       <c r="J39" t="n">
         <v>0.05497090428404448</v>
@@ -2947,7 +5963,7 @@
         <v>0.0425596085900067</v>
       </c>
       <c r="P39" t="n">
-        <v>0.6138753037553796</v>
+        <v>0.6138753037553797</v>
       </c>
       <c r="Q39" t="n">
         <v>1.588610259149604e-05</v>
@@ -2960,6 +5976,84 @@
       </c>
       <c r="T39" t="n">
         <v>0.002505415933532575</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>0.7492764727841064</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.000723527215893525</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>0.08423303439649957</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>0.6657669656035005</v>
       </c>
     </row>
     <row r="40">
@@ -2984,19 +6078,19 @@
         <v>1</v>
       </c>
       <c r="G40" t="n">
-        <v>0.9977869878946024</v>
+        <v>0.9978428920126018</v>
       </c>
       <c r="H40" t="n">
-        <v>0.00219955248324065</v>
+        <v>0.00214524925338305</v>
       </c>
       <c r="I40" t="n">
-        <v>1.338767802608433e-05</v>
+        <v>1.17867898844188e-05</v>
       </c>
       <c r="J40" t="n">
         <v>0.009468709671313349</v>
       </c>
       <c r="K40" t="n">
-        <v>0.4256057692906819</v>
+        <v>0.425605769290682</v>
       </c>
       <c r="L40" t="n">
         <v>0.02468124928288435</v>
@@ -3011,7 +6105,7 @@
         <v>0.06641729538733596</v>
       </c>
       <c r="P40" t="n">
-        <v>0.4150020531767503</v>
+        <v>0.4150020531767502</v>
       </c>
       <c r="Q40" t="n">
         <v>0.002241331754031618</v>
@@ -3024,6 +6118,84 @@
       </c>
       <c r="T40" t="n">
         <v>0.00190043600234145</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>0.4990940622388914</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.0009059377611086</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>0.0561535942356975</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>0.4438464057643025</v>
       </c>
     </row>
   </sheetData>

--- a/error_models/conv_models/nv_16x16_b1_dat-524288_wt-65536_int8/unique_complete_df.xlsx
+++ b/error_models/conv_models/nv_16x16_b1_dat-524288_wt-65536_int8/unique_complete_df.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unique_complete_layers" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,318 +425,323 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT40"/>
+  <dimension ref="A1:AV40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Layer</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Channels_in</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Channels_out</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Input_size</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Kernel_size</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Padding</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Masked</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>SDC</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Crash+Hang</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Single</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>FullChannels</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Rectangles</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>SingleChannelRandom</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>ShatteredChannel</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>QuasiShatteredChannel</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>MultiChannelBlock</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>BulletWake</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>SameRow</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>SingleBlock</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Skip4</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>same_row-single</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>same_row-multi</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>single_block-single</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>single_block-multi</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>quasi_shattered_channel-single</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>quasi_shattered_channel-multi</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>bullet_wake-single</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>bullet_wake-multi</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>skip_4-single</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>skip_4-multi</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>single_channel_alternated_blocks-single</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>single_channel_alternated_blocks-multi</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>multi_channel_block-single</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>multi_channel_block-multi</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>full_channels-single</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>full_channels-multi</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>single-single</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>single-multi</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>shattered_channel-single</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>shattered_channel-multi</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>single_channel_random-single</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>single_channel_random-multi</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>multiple_channels_uncategorized-single</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>multiple_channels_uncategorized-multi</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>rectangles-single</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>rectangles-multi</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="inlineStr">
         <is>
           <t>alexnet_cifar10_conv1</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="D2" t="n">
         <v>3</v>
       </c>
-      <c r="C2" t="n">
+      <c r="E2" t="n">
         <v>64</v>
       </c>
-      <c r="D2" t="n">
+      <c r="F2" t="n">
         <v>32</v>
       </c>
-      <c r="E2" t="n">
+      <c r="G2" t="n">
         <v>11</v>
       </c>
-      <c r="F2" t="n">
+      <c r="H2" t="n">
         <v>2</v>
       </c>
-      <c r="G2" t="n">
+      <c r="I2" t="n">
         <v>0.989938067577842</v>
       </c>
-      <c r="H2" t="n">
+      <c r="J2" t="n">
         <v>0.0100524652125198</v>
       </c>
-      <c r="I2" t="n">
+      <c r="K2" t="n">
         <v>9.395265507342336e-06</v>
       </c>
-      <c r="J2" t="n">
+      <c r="L2" t="n">
         <v>0.8301031552357492</v>
       </c>
-      <c r="K2" t="n">
+      <c r="M2" t="n">
         <v>0.0189381748847628</v>
       </c>
-      <c r="L2" t="n">
+      <c r="N2" t="n">
         <v>0.0696390579071479</v>
       </c>
-      <c r="M2" t="n">
+      <c r="O2" t="n">
         <v>1.186243919765209e-05</v>
       </c>
-      <c r="N2" t="n">
+      <c r="P2" t="n">
         <v>0.0464305673603416</v>
       </c>
-      <c r="O2" t="n">
+      <c r="Q2" t="n">
         <v>0.0348179874033044</v>
       </c>
-      <c r="P2" t="n">
+      <c r="R2" t="n">
         <v>2.764273054741316e-06</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="S2" t="n">
         <v>5.447570734181901e-05</v>
       </c>
-      <c r="R2" t="n">
+      <c r="T2" t="n">
         <v>2.548667490039243e-07</v>
       </c>
-      <c r="S2" t="n">
+      <c r="U2" t="n">
         <v>1.62797821995857e-06</v>
       </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
       <c r="V2" t="n">
         <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
@@ -745,13 +750,13 @@
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE2" t="n">
         <v>0</v>
@@ -763,7 +768,7 @@
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -772,105 +777,111 @@
         <v>1</v>
       </c>
       <c r="AK2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
       </c>
       <c r="AS2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU2" t="n">
         <v>0.1123068442346615</v>
       </c>
-      <c r="AT2" t="n">
+      <c r="AV2" t="n">
         <v>0.8876931557653385</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="inlineStr">
         <is>
           <t>alexnet_cifar10_conv2</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="D3" t="n">
         <v>64</v>
       </c>
-      <c r="C3" t="n">
+      <c r="E3" t="n">
         <v>192</v>
       </c>
-      <c r="D3" t="n">
+      <c r="F3" t="n">
         <v>12</v>
       </c>
-      <c r="E3" t="n">
+      <c r="G3" t="n">
         <v>5</v>
       </c>
-      <c r="F3" t="n">
+      <c r="H3" t="n">
         <v>2</v>
       </c>
-      <c r="G3" t="n">
+      <c r="I3" t="n">
         <v>0.9936335735313528</v>
       </c>
-      <c r="H3" t="n">
+      <c r="J3" t="n">
         <v>0.0063555372189197</v>
       </c>
-      <c r="I3" t="n">
+      <c r="K3" t="n">
         <v>1.081730559679619e-05</v>
       </c>
-      <c r="J3" t="n">
+      <c r="L3" t="n">
         <v>0.6655232138490071</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
         <v>0.1746988191661234</v>
       </c>
-      <c r="L3" t="n">
+      <c r="N3" t="n">
         <v>0.1145068476778056</v>
       </c>
-      <c r="M3" t="n">
+      <c r="O3" t="n">
         <v>0.0081266999554269</v>
       </c>
-      <c r="N3" t="n">
+      <c r="P3" t="n">
         <v>0.015612341874901</v>
       </c>
-      <c r="O3" t="n">
+      <c r="Q3" t="n">
         <v>0.0156080459740758</v>
       </c>
-      <c r="P3" t="n">
+      <c r="R3" t="n">
         <v>4.090382600848706e-06</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="S3" t="n">
         <v>0.005260536858786</v>
       </c>
-      <c r="R3" t="n">
+      <c r="T3" t="n">
         <v>0.0001804948833871</v>
       </c>
-      <c r="S3" t="n">
+      <c r="U3" t="n">
         <v>0.0003251189562066</v>
       </c>
-      <c r="T3" t="n">
+      <c r="V3" t="n">
         <v>0.0001537184775482</v>
       </c>
-      <c r="U3" t="n">
-        <v>1</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
       <c r="W3" t="n">
         <v>1</v>
       </c>
@@ -878,10 +889,10 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -890,13 +901,13 @@
         <v>1</v>
       </c>
       <c r="AC3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -905,7 +916,7 @@
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -914,105 +925,111 @@
         <v>1</v>
       </c>
       <c r="AK3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
       </c>
       <c r="AS3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU3" t="n">
         <v>0.1123065974034061</v>
       </c>
-      <c r="AT3" t="n">
+      <c r="AV3" t="n">
         <v>0.8876934025965939</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" t="inlineStr">
         <is>
           <t>alexnet_cifar10_conv3</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="D4" t="n">
         <v>192</v>
       </c>
-      <c r="C4" t="n">
+      <c r="E4" t="n">
         <v>384</v>
       </c>
-      <c r="D4" t="n">
+      <c r="F4" t="n">
         <v>5</v>
       </c>
-      <c r="E4" t="n">
+      <c r="G4" t="n">
         <v>3</v>
       </c>
-      <c r="F4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
         <v>0.998041028300635</v>
       </c>
-      <c r="H4" t="n">
+      <c r="J4" t="n">
         <v>0.001946591312892</v>
       </c>
-      <c r="I4" t="n">
+      <c r="K4" t="n">
         <v>1.230844234213843e-05</v>
       </c>
-      <c r="J4" t="n">
+      <c r="L4" t="n">
         <v>0.1376520177535577</v>
       </c>
-      <c r="K4" t="n">
+      <c r="M4" t="n">
         <v>0.6997218227144739</v>
       </c>
-      <c r="L4" t="n">
+      <c r="N4" t="n">
         <v>0.0398106591022519</v>
       </c>
-      <c r="M4" t="n">
+      <c r="O4" t="n">
         <v>0.008635358603917301</v>
       </c>
-      <c r="N4" t="n">
+      <c r="P4" t="n">
         <v>0.0970044837632127</v>
       </c>
-      <c r="O4" t="n">
+      <c r="Q4" t="n">
         <v>0.0143700933460622</v>
       </c>
-      <c r="P4" t="n">
+      <c r="R4" t="n">
         <v>1.566607317188105e-06</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="S4" t="n">
         <v>2.147544705948537e-05</v>
       </c>
-      <c r="R4" t="n">
+      <c r="T4" t="n">
         <v>0.0021962431725604</v>
       </c>
-      <c r="S4" t="n">
+      <c r="U4" t="n">
         <v>0.0002932538821028</v>
       </c>
-      <c r="T4" t="n">
+      <c r="V4" t="n">
         <v>0.0002929536633534</v>
       </c>
-      <c r="U4" t="n">
-        <v>1</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0</v>
-      </c>
       <c r="W4" t="n">
         <v>1</v>
       </c>
@@ -1020,10 +1037,10 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1032,22 +1049,22 @@
         <v>1</v>
       </c>
       <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE4" t="n">
         <v>0.9989303491014304</v>
       </c>
-      <c r="AD4" t="n">
+      <c r="AF4" t="n">
         <v>0.0010696508985694</v>
       </c>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0</v>
-      </c>
       <c r="AG4" t="n">
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1056,105 +1073,111 @@
         <v>1</v>
       </c>
       <c r="AK4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
       </c>
       <c r="AS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU4" t="n">
         <v>0.1123077430083088</v>
       </c>
-      <c r="AT4" t="n">
+      <c r="AV4" t="n">
         <v>0.8876922569916912</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" t="inlineStr">
         <is>
           <t>alexnet_cifar10_conv4</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="D5" t="n">
         <v>384</v>
       </c>
-      <c r="C5" t="n">
+      <c r="E5" t="n">
         <v>256</v>
       </c>
-      <c r="D5" t="n">
+      <c r="F5" t="n">
         <v>5</v>
       </c>
-      <c r="E5" t="n">
+      <c r="G5" t="n">
         <v>3</v>
       </c>
-      <c r="F5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
         <v>0.9960600443366232</v>
       </c>
-      <c r="H5" t="n">
+      <c r="J5" t="n">
         <v>0.0039280264296344</v>
       </c>
-      <c r="I5" t="n">
+      <c r="K5" t="n">
         <v>1.185728961150844e-05</v>
       </c>
-      <c r="J5" t="n">
+      <c r="L5" t="n">
         <v>0.296851487019159</v>
       </c>
-      <c r="K5" t="n">
+      <c r="M5" t="n">
         <v>0.5369724086304439</v>
       </c>
-      <c r="L5" t="n">
+      <c r="N5" t="n">
         <v>0.0673676715119646</v>
       </c>
-      <c r="M5" t="n">
+      <c r="O5" t="n">
         <v>0.011827257903436</v>
       </c>
-      <c r="N5" t="n">
+      <c r="P5" t="n">
         <v>0.0526983168472261</v>
       </c>
-      <c r="O5" t="n">
+      <c r="Q5" t="n">
         <v>0.0311345166214939</v>
       </c>
-      <c r="P5" t="n">
+      <c r="R5" t="n">
         <v>1.858717602755356e-06</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="S5" t="n">
         <v>1.14600168917194e-05</v>
       </c>
-      <c r="R5" t="n">
+      <c r="T5" t="n">
         <v>0.0018991213715449</v>
       </c>
-      <c r="S5" t="n">
+      <c r="U5" t="n">
         <v>0.0003529029398632</v>
       </c>
-      <c r="T5" t="n">
+      <c r="V5" t="n">
         <v>0.0008829264762429</v>
       </c>
-      <c r="U5" t="n">
-        <v>1</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
       <c r="W5" t="n">
         <v>1</v>
       </c>
@@ -1162,10 +1185,10 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1174,22 +1197,22 @@
         <v>1</v>
       </c>
       <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE5" t="n">
         <v>0.998929282587338</v>
       </c>
-      <c r="AD5" t="n">
+      <c r="AF5" t="n">
         <v>0.0010707174126619</v>
       </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
       <c r="AG5" t="n">
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1198,105 +1221,111 @@
         <v>1</v>
       </c>
       <c r="AK5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR5" t="n">
         <v>0</v>
       </c>
       <c r="AS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU5" t="n">
         <v>0.1123161279701659</v>
       </c>
-      <c r="AT5" t="n">
+      <c r="AV5" t="n">
         <v>0.887683872029834</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" t="inlineStr">
         <is>
           <t>alexnet_cifar10_conv5</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="D6" t="n">
         <v>256</v>
       </c>
-      <c r="C6" t="n">
+      <c r="E6" t="n">
         <v>256</v>
       </c>
-      <c r="D6" t="n">
+      <c r="F6" t="n">
         <v>5</v>
       </c>
-      <c r="E6" t="n">
+      <c r="G6" t="n">
         <v>3</v>
       </c>
-      <c r="F6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
         <v>0.9967934665800861</v>
       </c>
-      <c r="H6" t="n">
+      <c r="J6" t="n">
         <v>0.003194237520413</v>
       </c>
-      <c r="I6" t="n">
+      <c r="K6" t="n">
         <v>1.222395537010034e-05</v>
       </c>
-      <c r="J6" t="n">
+      <c r="L6" t="n">
         <v>0.3453130986944279</v>
       </c>
-      <c r="K6" t="n">
+      <c r="M6" t="n">
         <v>0.4984717530323768</v>
       </c>
-      <c r="L6" t="n">
+      <c r="N6" t="n">
         <v>0.0494725525552405</v>
       </c>
-      <c r="M6" t="n">
+      <c r="O6" t="n">
         <v>0.0075143602966897</v>
       </c>
-      <c r="N6" t="n">
+      <c r="P6" t="n">
         <v>0.0721715683957514</v>
       </c>
-      <c r="O6" t="n">
+      <c r="Q6" t="n">
         <v>0.0229602946666208</v>
       </c>
-      <c r="P6" t="n">
+      <c r="R6" t="n">
         <v>1.003086683818171e-06</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="S6" t="n">
         <v>1.055683639850125e-05</v>
       </c>
-      <c r="R6" t="n">
+      <c r="T6" t="n">
         <v>0.0032680915135873</v>
       </c>
-      <c r="S6" t="n">
+      <c r="U6" t="n">
         <v>0.0001087330834002</v>
       </c>
-      <c r="T6" t="n">
+      <c r="V6" t="n">
         <v>0.000707915894692</v>
       </c>
-      <c r="U6" t="n">
-        <v>1</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
       <c r="W6" t="n">
         <v>1</v>
       </c>
@@ -1304,10 +1333,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1316,22 +1345,22 @@
         <v>1</v>
       </c>
       <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE6" t="n">
         <v>0.9981805648057058</v>
       </c>
-      <c r="AD6" t="n">
+      <c r="AF6" t="n">
         <v>0.0018194351942942</v>
       </c>
-      <c r="AE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>0</v>
-      </c>
       <c r="AG6" t="n">
         <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1340,105 +1369,111 @@
         <v>1</v>
       </c>
       <c r="AK6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
       </c>
       <c r="AS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU6" t="n">
         <v>0.1123161067701795</v>
       </c>
-      <c r="AT6" t="n">
+      <c r="AV6" t="n">
         <v>0.8876838932298206</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" t="inlineStr">
         <is>
           <t>lenet_cifar10_conv1</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="D7" t="n">
         <v>3</v>
       </c>
-      <c r="C7" t="n">
+      <c r="E7" t="n">
         <v>32</v>
       </c>
-      <c r="D7" t="n">
+      <c r="F7" t="n">
         <v>32</v>
       </c>
-      <c r="E7" t="n">
+      <c r="G7" t="n">
         <v>3</v>
       </c>
-      <c r="F7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
         <v>0.9861272350558278</v>
       </c>
-      <c r="H7" t="n">
+      <c r="J7" t="n">
         <v>0.0138613526319897</v>
       </c>
-      <c r="I7" t="n">
+      <c r="K7" t="n">
         <v>1.134036805168828e-05</v>
       </c>
-      <c r="J7" t="n">
+      <c r="L7" t="n">
         <v>0.8300939230624722</v>
       </c>
-      <c r="K7" t="n">
+      <c r="M7" t="n">
         <v>0.0237932077100839</v>
       </c>
-      <c r="L7" t="n">
+      <c r="N7" t="n">
         <v>0.0340772367786082</v>
       </c>
-      <c r="M7" t="n">
+      <c r="O7" t="n">
         <v>1.100436527133691e-05</v>
       </c>
-      <c r="N7" t="n">
+      <c r="P7" t="n">
         <v>0.0584141604623468</v>
       </c>
-      <c r="O7" t="n">
+      <c r="Q7" t="n">
         <v>0.038936320527257</v>
       </c>
-      <c r="P7" t="n">
+      <c r="R7" t="n">
         <v>5.008058271858581e-06</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="S7" t="n">
         <v>0.0146660279519363</v>
       </c>
-      <c r="R7" t="n">
+      <c r="T7" t="n">
         <v>4.120928897450623e-07</v>
       </c>
-      <c r="S7" t="n">
+      <c r="U7" t="n">
         <v>1.490115119506455e-06</v>
       </c>
-      <c r="T7" t="n">
+      <c r="V7" t="n">
         <v>1.13693161209331e-06</v>
       </c>
-      <c r="U7" t="n">
-        <v>1</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
       <c r="W7" t="n">
         <v>1</v>
       </c>
@@ -1446,7 +1481,7 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
@@ -1455,7 +1490,7 @@
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1467,13 +1502,13 @@
         <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1482,105 +1517,111 @@
         <v>1</v>
       </c>
       <c r="AK7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
       </c>
       <c r="AS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="n">
         <v>0.1123071268636662</v>
       </c>
-      <c r="AT7" t="n">
+      <c r="AV7" t="n">
         <v>0.8876928731363338</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="n">
+        <v>6</v>
+      </c>
+      <c r="C8" t="inlineStr">
         <is>
           <t>lenet_cifar10_conv2</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="D8" t="n">
         <v>32</v>
       </c>
-      <c r="C8" t="n">
+      <c r="E8" t="n">
         <v>64</v>
       </c>
-      <c r="D8" t="n">
+      <c r="F8" t="n">
         <v>16</v>
       </c>
-      <c r="E8" t="n">
+      <c r="G8" t="n">
         <v>3</v>
       </c>
-      <c r="F8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
         <v>0.9950562533293884</v>
       </c>
-      <c r="H8" t="n">
+      <c r="J8" t="n">
         <v>0.0049326674122344</v>
       </c>
-      <c r="I8" t="n">
+      <c r="K8" t="n">
         <v>1.100731424655236e-05</v>
       </c>
-      <c r="J8" t="n">
+      <c r="L8" t="n">
         <v>0.8123051446570934</v>
       </c>
-      <c r="K8" t="n">
+      <c r="M8" t="n">
         <v>0.0289476905017699</v>
       </c>
-      <c r="L8" t="n">
+      <c r="N8" t="n">
         <v>0.07383884195623371</v>
       </c>
-      <c r="M8" t="n">
+      <c r="O8" t="n">
         <v>0.0076715381290013</v>
       </c>
-      <c r="N8" t="n">
+      <c r="P8" t="n">
         <v>0.0513697540726642</v>
       </c>
-      <c r="O8" t="n">
+      <c r="Q8" t="n">
         <v>0.0160511924168967</v>
       </c>
-      <c r="P8" t="n">
+      <c r="R8" t="n">
         <v>4.549414023256445e-06</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="S8" t="n">
         <v>0.0064660803090688</v>
       </c>
-      <c r="R8" t="n">
+      <c r="T8" t="n">
         <v>3.456745500944262e-06</v>
       </c>
-      <c r="S8" t="n">
+      <c r="U8" t="n">
         <v>9.05517997509338e-06</v>
       </c>
-      <c r="T8" t="n">
+      <c r="V8" t="n">
         <v>0.0033326246736416</v>
       </c>
-      <c r="U8" t="n">
-        <v>1</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
       <c r="W8" t="n">
         <v>1</v>
       </c>
@@ -1588,10 +1629,10 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1609,13 +1650,13 @@
         <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1624,105 +1665,111 @@
         <v>1</v>
       </c>
       <c r="AK8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR8" t="n">
         <v>0</v>
       </c>
       <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="n">
         <v>0.1123072296378497</v>
       </c>
-      <c r="AT8" t="n">
+      <c r="AV8" t="n">
         <v>0.8876927703621503</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="A9" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="n">
+        <v>7</v>
+      </c>
+      <c r="C9" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.1.conv.1</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="D9" t="n">
         <v>32</v>
       </c>
-      <c r="C9" t="n">
+      <c r="E9" t="n">
         <v>16</v>
       </c>
-      <c r="D9" t="n">
+      <c r="F9" t="n">
         <v>16</v>
       </c>
-      <c r="E9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
       <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
         <v>0.9979818033372152</v>
       </c>
-      <c r="H9" t="n">
+      <c r="J9" t="n">
         <v>0.0020046124804475</v>
       </c>
-      <c r="I9" t="n">
+      <c r="K9" t="n">
         <v>1.351223820642841e-05</v>
       </c>
-      <c r="J9" t="n">
+      <c r="L9" t="n">
         <v>0.8133054747516359</v>
       </c>
-      <c r="K9" t="n">
+      <c r="M9" t="n">
         <v>0.034131159110866</v>
       </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
         <v>0.0016030032724046</v>
       </c>
-      <c r="N9" t="n">
+      <c r="P9" t="n">
         <v>8.039723861453795e-06</v>
       </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
         <v>8.489157587513266e-06</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="S9" t="n">
         <v>0.150930222823956</v>
       </c>
-      <c r="R9" t="n">
+      <c r="T9" t="n">
         <v>2.705314406728949e-06</v>
       </c>
-      <c r="S9" t="n">
+      <c r="U9" t="n">
         <v>1.071379607310488e-05</v>
       </c>
-      <c r="T9" t="n">
+      <c r="V9" t="n">
         <v>1.201050778277717e-07</v>
       </c>
-      <c r="U9" t="n">
-        <v>1</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
       <c r="W9" t="n">
         <v>1</v>
       </c>
@@ -1730,7 +1777,7 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z9" t="n">
         <v>0</v>
@@ -1739,13 +1786,13 @@
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
@@ -1757,7 +1804,7 @@
         <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1766,25 +1813,25 @@
         <v>1</v>
       </c>
       <c r="AK9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR9" t="n">
         <v>0</v>
@@ -1793,80 +1840,86 @@
         <v>0</v>
       </c>
       <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV9" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="A10" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="n">
+        <v>8</v>
+      </c>
+      <c r="C10" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.10.conv.2</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="D10" t="n">
         <v>384</v>
       </c>
-      <c r="C10" t="n">
+      <c r="E10" t="n">
         <v>64</v>
       </c>
-      <c r="D10" t="n">
+      <c r="F10" t="n">
         <v>8</v>
       </c>
-      <c r="E10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
       <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
         <v>0.9992123452401048</v>
       </c>
-      <c r="H10" t="n">
+      <c r="J10" t="n">
         <v>0.00077555111694</v>
       </c>
-      <c r="I10" t="n">
+      <c r="K10" t="n">
         <v>1.203169882427591e-05</v>
       </c>
-      <c r="J10" t="n">
+      <c r="L10" t="n">
         <v>0.0034157852262598</v>
       </c>
-      <c r="K10" t="n">
+      <c r="M10" t="n">
         <v>0.8909289871033365</v>
       </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
         <v>0.0029792323513782</v>
       </c>
-      <c r="N10" t="n">
+      <c r="P10" t="n">
         <v>1.018113030023754e-05</v>
       </c>
-      <c r="O10" t="n">
+      <c r="Q10" t="n">
         <v>1.283507701496675e-07</v>
       </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
         <v>0.1006200496246514</v>
       </c>
-      <c r="R10" t="n">
+      <c r="T10" t="n">
         <v>0.0020455642691726</v>
       </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
       <c r="U10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1881,13 +1934,13 @@
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>
@@ -1905,28 +1958,28 @@
         <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR10" t="n">
         <v>0</v>
@@ -1935,80 +1988,86 @@
         <v>0</v>
       </c>
       <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV10" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+      <c r="A11" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="n">
+        <v>9</v>
+      </c>
+      <c r="C11" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.12.conv.0.0</t>
         </is>
       </c>
-      <c r="B11" t="n">
+      <c r="D11" t="n">
         <v>96</v>
       </c>
-      <c r="C11" t="n">
+      <c r="E11" t="n">
         <v>576</v>
       </c>
-      <c r="D11" t="n">
+      <c r="F11" t="n">
         <v>8</v>
       </c>
-      <c r="E11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
       <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
         <v>0.9997790829556183</v>
       </c>
-      <c r="H11" t="n">
+      <c r="J11" t="n">
         <v>0.0002083405365856</v>
       </c>
-      <c r="I11" t="n">
+      <c r="K11" t="n">
         <v>1.250456366512909e-05</v>
       </c>
-      <c r="J11" t="n">
+      <c r="L11" t="n">
         <v>0.0014613408283693</v>
       </c>
-      <c r="K11" t="n">
+      <c r="M11" t="n">
         <v>0.982487798418188</v>
       </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
         <v>0.0004430480130373</v>
       </c>
-      <c r="N11" t="n">
+      <c r="P11" t="n">
         <v>6.832494497582256e-06</v>
       </c>
-      <c r="O11" t="n">
+      <c r="Q11" t="n">
         <v>5.949476414616127e-08</v>
       </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
         <v>0.015144960638079</v>
       </c>
-      <c r="R11" t="n">
+      <c r="T11" t="n">
         <v>0.0004558881689338</v>
       </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
       <c r="U11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -2017,7 +2076,7 @@
         <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -2029,7 +2088,7 @@
         <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE11" t="n">
         <v>0</v>
@@ -2047,28 +2106,28 @@
         <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR11" t="n">
         <v>0</v>
@@ -2077,78 +2136,84 @@
         <v>0</v>
       </c>
       <c r="AT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV11" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="n">
+        <v>10</v>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.2.conv.2</t>
         </is>
       </c>
-      <c r="B12" t="n">
+      <c r="D12" t="n">
         <v>96</v>
       </c>
-      <c r="C12" t="n">
+      <c r="E12" t="n">
         <v>24</v>
       </c>
-      <c r="D12" t="n">
+      <c r="F12" t="n">
         <v>8</v>
       </c>
-      <c r="E12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
       <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
         <v>0.998633020725647</v>
       </c>
-      <c r="H12" t="n">
+      <c r="J12" t="n">
         <v>0.0013537488929388</v>
       </c>
-      <c r="I12" t="n">
+      <c r="K12" t="n">
         <v>1.315843728348307e-05</v>
       </c>
-      <c r="J12" t="n">
+      <c r="L12" t="n">
         <v>0.45633503951514</v>
       </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
         <v>8.121670648778614e-08</v>
       </c>
-      <c r="M12" t="n">
+      <c r="O12" t="n">
         <v>0.0042329303512806</v>
       </c>
-      <c r="N12" t="n">
+      <c r="P12" t="n">
         <v>4.342563558856337e-06</v>
       </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
         <v>0.375874452677238</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="S12" t="n">
         <v>0.1509414365868097</v>
       </c>
-      <c r="R12" t="n">
+      <c r="T12" t="n">
         <v>6.670975889542532e-06</v>
       </c>
-      <c r="S12" t="n">
+      <c r="U12" t="n">
         <v>0.0126026736175113</v>
       </c>
-      <c r="T12" t="n">
+      <c r="V12" t="n">
         <v>2.300551734483913e-06</v>
       </c>
-      <c r="U12" t="n">
-        <v>1</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
       <c r="W12" t="n">
         <v>1</v>
       </c>
@@ -2156,7 +2221,7 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z12" t="n">
         <v>0</v>
@@ -2165,13 +2230,13 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE12" t="n">
         <v>0</v>
@@ -2183,7 +2248,7 @@
         <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2192,25 +2257,25 @@
         <v>1</v>
       </c>
       <c r="AK12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR12" t="n">
         <v>0</v>
@@ -2219,78 +2284,84 @@
         <v>0</v>
       </c>
       <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV12" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+      <c r="A13" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="n">
+        <v>11</v>
+      </c>
+      <c r="C13" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.3.conv.0.0</t>
         </is>
       </c>
-      <c r="B13" t="n">
+      <c r="D13" t="n">
         <v>24</v>
       </c>
-      <c r="C13" t="n">
+      <c r="E13" t="n">
         <v>144</v>
       </c>
-      <c r="D13" t="n">
+      <c r="F13" t="n">
         <v>8</v>
       </c>
-      <c r="E13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
       <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
         <v>0.9992513280379915</v>
       </c>
-      <c r="H13" t="n">
+      <c r="J13" t="n">
         <v>0.0007357537838654</v>
       </c>
-      <c r="I13" t="n">
+      <c r="K13" t="n">
         <v>1.28462340120047e-05</v>
       </c>
-      <c r="J13" t="n">
+      <c r="L13" t="n">
         <v>0.5653425193494623</v>
       </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
       <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
         <v>4.421110711368516e-06</v>
       </c>
-      <c r="N13" t="n">
+      <c r="P13" t="n">
         <v>6.159181852935528e-06</v>
       </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
         <v>0.3656000191618176</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="S13" t="n">
         <v>0.0604012334079266</v>
       </c>
-      <c r="R13" t="n">
+      <c r="T13" t="n">
         <v>6.742960119419726e-06</v>
       </c>
-      <c r="S13" t="n">
+      <c r="U13" t="n">
         <v>0.0086387604693321</v>
       </c>
-      <c r="T13" t="n">
+      <c r="V13" t="n">
         <v>7.241464673763863e-08</v>
       </c>
-      <c r="U13" t="n">
-        <v>1</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
       <c r="W13" t="n">
         <v>1</v>
       </c>
@@ -2298,7 +2369,7 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z13" t="n">
         <v>0</v>
@@ -2307,13 +2378,13 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE13" t="n">
         <v>0</v>
@@ -2325,7 +2396,7 @@
         <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2334,25 +2405,25 @@
         <v>1</v>
       </c>
       <c r="AK13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR13" t="n">
         <v>0</v>
@@ -2361,78 +2432,84 @@
         <v>0</v>
       </c>
       <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV13" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
+      <c r="A14" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="n">
+        <v>12</v>
+      </c>
+      <c r="C14" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.3.conv.2</t>
         </is>
       </c>
-      <c r="B14" t="n">
+      <c r="D14" t="n">
         <v>144</v>
       </c>
-      <c r="C14" t="n">
+      <c r="E14" t="n">
         <v>24</v>
       </c>
-      <c r="D14" t="n">
+      <c r="F14" t="n">
         <v>4</v>
       </c>
-      <c r="E14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
       <c r="G14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
         <v>0.9980101902429822</v>
       </c>
-      <c r="H14" t="n">
+      <c r="J14" t="n">
         <v>0.0019768368364713</v>
       </c>
-      <c r="I14" t="n">
+      <c r="K14" t="n">
         <v>1.290097641579972e-05</v>
       </c>
-      <c r="J14" t="n">
+      <c r="L14" t="n">
         <v>0.259768404538699</v>
       </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
       <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
         <v>0.0092487112062069</v>
       </c>
-      <c r="N14" t="n">
+      <c r="P14" t="n">
         <v>4.640027434245517e-06</v>
       </c>
-      <c r="O14" t="n">
+      <c r="Q14" t="n">
         <v>1.519267119223007e-08</v>
       </c>
-      <c r="P14" t="n">
+      <c r="R14" t="n">
         <v>0.5708113015588091</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="S14" t="n">
         <v>0.15093319395818</v>
       </c>
-      <c r="R14" t="n">
+      <c r="T14" t="n">
         <v>7.758752735472552e-06</v>
       </c>
-      <c r="S14" t="n">
+      <c r="U14" t="n">
         <v>0.009224277622748999</v>
       </c>
-      <c r="T14" t="n">
+      <c r="V14" t="n">
         <v>1.625198384158754e-06</v>
       </c>
-      <c r="U14" t="n">
-        <v>1</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0</v>
-      </c>
       <c r="W14" t="n">
         <v>1</v>
       </c>
@@ -2440,7 +2517,7 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z14" t="n">
         <v>0</v>
@@ -2449,13 +2526,13 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE14" t="n">
         <v>0</v>
@@ -2467,7 +2544,7 @@
         <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2476,25 +2553,25 @@
         <v>1</v>
       </c>
       <c r="AK14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR14" t="n">
         <v>0</v>
@@ -2503,75 +2580,81 @@
         <v>0</v>
       </c>
       <c r="AT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV14" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+      <c r="A15" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="n">
+        <v>13</v>
+      </c>
+      <c r="C15" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.4.conv.0.0</t>
         </is>
       </c>
-      <c r="B15" t="n">
+      <c r="D15" t="n">
         <v>24</v>
       </c>
-      <c r="C15" t="n">
+      <c r="E15" t="n">
         <v>144</v>
       </c>
-      <c r="D15" t="n">
+      <c r="F15" t="n">
         <v>4</v>
       </c>
-      <c r="E15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
       <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
         <v>0.9995871251755344</v>
       </c>
-      <c r="H15" t="n">
+      <c r="J15" t="n">
         <v>0.0003999668504629</v>
       </c>
-      <c r="I15" t="n">
+      <c r="K15" t="n">
         <v>1.283602987200232e-05</v>
       </c>
-      <c r="J15" t="n">
+      <c r="L15" t="n">
         <v>0.2683870752884121</v>
       </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
       <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
         <v>3.228363042356206e-06</v>
       </c>
-      <c r="N15" t="n">
+      <c r="P15" t="n">
         <v>6.055568356780883e-06</v>
       </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
         <v>0.6366090059445582</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="S15" t="n">
         <v>0.08235059551402089</v>
       </c>
-      <c r="R15" t="n">
+      <c r="T15" t="n">
         <v>5.979756385316338e-06</v>
       </c>
-      <c r="S15" t="n">
+      <c r="U15" t="n">
         <v>0.0126379876210933</v>
       </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1</v>
-      </c>
       <c r="V15" t="n">
         <v>0</v>
       </c>
@@ -2582,7 +2665,7 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z15" t="n">
         <v>0</v>
@@ -2591,13 +2674,13 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE15" t="n">
         <v>0</v>
@@ -2609,7 +2692,7 @@
         <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2618,25 +2701,25 @@
         <v>1</v>
       </c>
       <c r="AK15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR15" t="n">
         <v>0</v>
@@ -2645,75 +2728,81 @@
         <v>0</v>
       </c>
       <c r="AT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
+      <c r="A16" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="n">
+        <v>14</v>
+      </c>
+      <c r="C16" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.5.conv.0.0</t>
         </is>
       </c>
-      <c r="B16" t="n">
+      <c r="D16" t="n">
         <v>32</v>
       </c>
-      <c r="C16" t="n">
+      <c r="E16" t="n">
         <v>192</v>
       </c>
-      <c r="D16" t="n">
+      <c r="F16" t="n">
         <v>4</v>
       </c>
-      <c r="E16" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
       <c r="G16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
         <v>0.999823703362223</v>
       </c>
-      <c r="H16" t="n">
+      <c r="J16" t="n">
         <v>0.000164662249148</v>
       </c>
-      <c r="I16" t="n">
+      <c r="K16" t="n">
         <v>1.156244449812495e-05</v>
       </c>
-      <c r="J16" t="n">
+      <c r="L16" t="n">
         <v>0.0002036607974802</v>
       </c>
-      <c r="K16" t="n">
+      <c r="M16" t="n">
         <v>1.021723299676695e-05</v>
       </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
         <v>2.036227992156178e-05</v>
       </c>
-      <c r="N16" t="n">
+      <c r="P16" t="n">
         <v>1.244328926157445e-05</v>
       </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
         <v>0.9244544404151054</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="S16" t="n">
         <v>0.0603999406241808</v>
       </c>
-      <c r="R16" t="n">
+      <c r="T16" t="n">
         <v>1.310726620129549e-05</v>
       </c>
-      <c r="S16" t="n">
+      <c r="U16" t="n">
         <v>0.0148857561507216</v>
       </c>
-      <c r="T16" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1</v>
-      </c>
       <c r="V16" t="n">
         <v>0</v>
       </c>
@@ -2724,7 +2813,7 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z16" t="n">
         <v>0</v>
@@ -2733,13 +2822,13 @@
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE16" t="n">
         <v>0</v>
@@ -2751,7 +2840,7 @@
         <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2760,25 +2849,25 @@
         <v>1</v>
       </c>
       <c r="AK16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR16" t="n">
         <v>0</v>
@@ -2787,78 +2876,84 @@
         <v>0</v>
       </c>
       <c r="AT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV16" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="inlineStr">
+      <c r="A17" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="n">
+        <v>15</v>
+      </c>
+      <c r="C17" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.5.conv.2</t>
         </is>
       </c>
-      <c r="B17" t="n">
+      <c r="D17" t="n">
         <v>192</v>
       </c>
-      <c r="C17" t="n">
+      <c r="E17" t="n">
         <v>32</v>
       </c>
-      <c r="D17" t="n">
+      <c r="F17" t="n">
         <v>2</v>
       </c>
-      <c r="E17" t="n">
-        <v>1</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
       <c r="G17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
         <v>0.9989937428205226</v>
       </c>
-      <c r="H17" t="n">
+      <c r="J17" t="n">
         <v>0.0009938038433056</v>
       </c>
-      <c r="I17" t="n">
+      <c r="K17" t="n">
         <v>1.238139204092512e-05</v>
       </c>
-      <c r="J17" t="n">
+      <c r="L17" t="n">
         <v>0.1185343048526066</v>
       </c>
-      <c r="K17" t="n">
+      <c r="M17" t="n">
         <v>0.0009623242279945999</v>
       </c>
-      <c r="L17" t="n">
+      <c r="N17" t="n">
         <v>0.0002398853511684</v>
       </c>
-      <c r="M17" t="n">
+      <c r="O17" t="n">
         <v>0.0098364845784428</v>
       </c>
-      <c r="N17" t="n">
+      <c r="P17" t="n">
         <v>9.123431043753115e-06</v>
       </c>
-      <c r="O17" t="n">
+      <c r="Q17" t="n">
         <v>8.409054246782047e-09</v>
       </c>
-      <c r="P17" t="n">
+      <c r="R17" t="n">
         <v>0.7209284435398771</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="S17" t="n">
         <v>0.1425297993636328</v>
       </c>
-      <c r="R17" t="n">
+      <c r="T17" t="n">
         <v>0.0009694348357847</v>
       </c>
-      <c r="S17" t="n">
+      <c r="U17" t="n">
         <v>0.0052649073104832</v>
       </c>
-      <c r="T17" t="n">
+      <c r="V17" t="n">
         <v>0.0007252121557806</v>
       </c>
-      <c r="U17" t="n">
-        <v>1</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
       <c r="W17" t="n">
         <v>1</v>
       </c>
@@ -2866,7 +2961,7 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z17" t="n">
         <v>0</v>
@@ -2875,16 +2970,16 @@
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -2893,7 +2988,7 @@
         <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2902,105 +2997,111 @@
         <v>1</v>
       </c>
       <c r="AK17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR17" t="n">
         <v>0</v>
       </c>
       <c r="AS17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="inlineStr">
+      <c r="A18" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="n">
+        <v>16</v>
+      </c>
+      <c r="C18" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.6.conv.0.0</t>
         </is>
       </c>
-      <c r="B18" t="n">
+      <c r="D18" t="n">
         <v>32</v>
       </c>
-      <c r="C18" t="n">
+      <c r="E18" t="n">
         <v>192</v>
       </c>
-      <c r="D18" t="n">
+      <c r="F18" t="n">
         <v>2</v>
       </c>
-      <c r="E18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
       <c r="G18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
         <v>0.9997876940183806</v>
       </c>
-      <c r="H18" t="n">
+      <c r="J18" t="n">
         <v>0.0002003691030704</v>
       </c>
-      <c r="I18" t="n">
+      <c r="K18" t="n">
         <v>1.186493441820197e-05</v>
       </c>
-      <c r="J18" t="n">
+      <c r="L18" t="n">
         <v>0.08317730312664109</v>
       </c>
-      <c r="K18" t="n">
+      <c r="M18" t="n">
         <v>1.486827160216846e-05</v>
       </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
         <v>0.001201203064455</v>
       </c>
-      <c r="N18" t="n">
+      <c r="P18" t="n">
         <v>1.313590241928479e-05</v>
       </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
         <v>0.8613462914868761</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="S18" t="n">
         <v>0.0411972980229036</v>
       </c>
-      <c r="R18" t="n">
+      <c r="T18" t="n">
         <v>1.516231004748147e-05</v>
       </c>
-      <c r="S18" t="n">
+      <c r="U18" t="n">
         <v>0.0130343587065509</v>
       </c>
-      <c r="T18" t="n">
+      <c r="V18" t="n">
         <v>3.071643734142219e-07</v>
       </c>
-      <c r="U18" t="n">
-        <v>1</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
       <c r="W18" t="n">
         <v>1</v>
       </c>
@@ -3008,7 +3109,7 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z18" t="n">
         <v>0</v>
@@ -3017,13 +3118,13 @@
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
@@ -3035,7 +3136,7 @@
         <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -3044,25 +3145,25 @@
         <v>1</v>
       </c>
       <c r="AK18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR18" t="n">
         <v>0</v>
@@ -3071,80 +3172,86 @@
         <v>0</v>
       </c>
       <c r="AT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV18" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="inlineStr">
+      <c r="A19" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="n">
+        <v>17</v>
+      </c>
+      <c r="C19" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.7.conv.2</t>
         </is>
       </c>
-      <c r="B19" t="n">
+      <c r="D19" t="n">
         <v>192</v>
       </c>
-      <c r="C19" t="n">
+      <c r="E19" t="n">
         <v>64</v>
       </c>
-      <c r="D19" t="n">
+      <c r="F19" t="n">
         <v>2</v>
       </c>
-      <c r="E19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
       <c r="G19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
         <v>0.9994269673805618</v>
       </c>
-      <c r="H19" t="n">
+      <c r="J19" t="n">
         <v>0.0005605480318403001</v>
       </c>
-      <c r="I19" t="n">
+      <c r="K19" t="n">
         <v>1.241264346720166e-05</v>
       </c>
-      <c r="J19" t="n">
+      <c r="L19" t="n">
         <v>0.0556772342928949</v>
       </c>
-      <c r="K19" t="n">
+      <c r="M19" t="n">
         <v>0.873173913045262</v>
       </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
         <v>0.0012521894084422</v>
       </c>
-      <c r="N19" t="n">
+      <c r="P19" t="n">
         <v>9.606785153624129e-06</v>
       </c>
-      <c r="O19" t="n">
+      <c r="Q19" t="n">
         <v>2.074606344836537e-08</v>
       </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
         <v>0.068623868090923</v>
       </c>
-      <c r="R19" t="n">
+      <c r="T19" t="n">
         <v>0.0012630956871298</v>
       </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
       <c r="U19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -3159,13 +3266,13 @@
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -3183,28 +3290,28 @@
         <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR19" t="n">
         <v>0</v>
@@ -3213,80 +3320,86 @@
         <v>0</v>
       </c>
       <c r="AT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV19" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="inlineStr">
+      <c r="A20" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="n">
+        <v>18</v>
+      </c>
+      <c r="C20" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.8.conv.0.0</t>
         </is>
       </c>
-      <c r="B20" t="n">
+      <c r="D20" t="n">
         <v>64</v>
       </c>
-      <c r="C20" t="n">
+      <c r="E20" t="n">
         <v>384</v>
       </c>
-      <c r="D20" t="n">
+      <c r="F20" t="n">
         <v>2</v>
       </c>
-      <c r="E20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
       <c r="G20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
         <v>0.9998428001068322</v>
       </c>
-      <c r="H20" t="n">
+      <c r="J20" t="n">
         <v>0.0001453265810242</v>
       </c>
-      <c r="I20" t="n">
+      <c r="K20" t="n">
         <v>1.180136801295648e-05</v>
       </c>
-      <c r="J20" t="n">
+      <c r="L20" t="n">
         <v>0.0001750162828316</v>
       </c>
-      <c r="K20" t="n">
+      <c r="M20" t="n">
         <v>0.983997564511728</v>
       </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
         <v>4.57249790560786e-06</v>
       </c>
-      <c r="N20" t="n">
+      <c r="P20" t="n">
         <v>1.047885323945237e-05</v>
       </c>
-      <c r="O20" t="n">
+      <c r="Q20" t="n">
         <v>3.369646027924598e-08</v>
       </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
         <v>0.0151253871470411</v>
       </c>
-      <c r="R20" t="n">
+      <c r="T20" t="n">
         <v>0.000686875066663</v>
       </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
       <c r="U20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -3301,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -3325,28 +3438,28 @@
         <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR20" t="n">
         <v>0</v>
@@ -3355,80 +3468,86 @@
         <v>0</v>
       </c>
       <c r="AT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV20" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="inlineStr">
+      <c r="A21" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="n">
+        <v>19</v>
+      </c>
+      <c r="C21" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.9.conv.2</t>
         </is>
       </c>
-      <c r="B21" t="n">
+      <c r="D21" t="n">
         <v>384</v>
       </c>
-      <c r="C21" t="n">
+      <c r="E21" t="n">
         <v>64</v>
       </c>
-      <c r="D21" t="n">
+      <c r="F21" t="n">
         <v>2</v>
       </c>
-      <c r="E21" t="n">
-        <v>1</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
       <c r="G21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
         <v>0.9990872820628892</v>
       </c>
-      <c r="H21" t="n">
+      <c r="J21" t="n">
         <v>0.0009001459986948</v>
       </c>
-      <c r="I21" t="n">
+      <c r="K21" t="n">
         <v>1.249999428529224e-05</v>
       </c>
-      <c r="J21" t="n">
+      <c r="L21" t="n">
         <v>0.0176177432633315</v>
       </c>
-      <c r="K21" t="n">
+      <c r="M21" t="n">
         <v>0.8760743736687528</v>
       </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
         <v>0.0032392287281422</v>
       </c>
-      <c r="N21" t="n">
+      <c r="P21" t="n">
         <v>9.830337200406028e-06</v>
       </c>
-      <c r="O21" t="n">
+      <c r="Q21" t="n">
         <v>2.517766164321582e-07</v>
       </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
         <v>0.1006171498048963</v>
       </c>
-      <c r="R21" t="n">
+      <c r="T21" t="n">
         <v>0.0024413504769293</v>
       </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0</v>
-      </c>
       <c r="U21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -3443,13 +3562,13 @@
         <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -3467,28 +3586,28 @@
         <v>0</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR21" t="n">
         <v>0</v>
@@ -3497,72 +3616,78 @@
         <v>0</v>
       </c>
       <c r="AT21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV21" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
+      <c r="A22" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="n">
+        <v>20</v>
+      </c>
+      <c r="C22" t="inlineStr">
         <is>
           <t>res50_cifar10_layer1.2.conv1</t>
         </is>
       </c>
-      <c r="B22" t="n">
+      <c r="D22" t="n">
         <v>256</v>
       </c>
-      <c r="C22" t="n">
+      <c r="E22" t="n">
         <v>64</v>
       </c>
-      <c r="D22" t="n">
+      <c r="F22" t="n">
         <v>32</v>
       </c>
-      <c r="E22" t="n">
-        <v>1</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
       <c r="G22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
         <v>0.6047956804734581</v>
       </c>
-      <c r="H22" t="n">
+      <c r="J22" t="n">
         <v>0.3951914885139226</v>
       </c>
-      <c r="I22" t="n">
+      <c r="K22" t="n">
         <v>1.275906848857813e-05</v>
       </c>
-      <c r="J22" t="n">
+      <c r="L22" t="n">
         <v>0.0019859783867124</v>
       </c>
-      <c r="K22" t="n">
+      <c r="M22" t="n">
         <v>0.992607957682441</v>
       </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
         <v>5.825431977969821e-06</v>
       </c>
-      <c r="N22" t="n">
+      <c r="P22" t="n">
         <v>5.278610976742587e-08</v>
       </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
         <v>1.395266449197736e-08</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="S22" t="n">
         <v>0.005399955570659</v>
       </c>
-      <c r="R22" t="n">
+      <c r="T22" t="n">
         <v>1.442453043886883e-07</v>
       </c>
-      <c r="S22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0</v>
-      </c>
       <c r="U22" t="n">
         <v>0</v>
       </c>
@@ -3585,13 +3710,13 @@
         <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
@@ -3603,7 +3728,7 @@
         <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3612,25 +3737,25 @@
         <v>1</v>
       </c>
       <c r="AK22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR22" t="n">
         <v>0</v>
@@ -3639,75 +3764,81 @@
         <v>0</v>
       </c>
       <c r="AT22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="inlineStr">
+      <c r="A23" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="n">
+        <v>21</v>
+      </c>
+      <c r="C23" t="inlineStr">
         <is>
           <t>res50_cifar10_layer2.1.conv1</t>
         </is>
       </c>
-      <c r="B23" t="n">
+      <c r="D23" t="n">
         <v>512</v>
       </c>
-      <c r="C23" t="n">
+      <c r="E23" t="n">
         <v>128</v>
       </c>
-      <c r="D23" t="n">
+      <c r="F23" t="n">
         <v>16</v>
       </c>
-      <c r="E23" t="n">
-        <v>1</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
       <c r="G23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
         <v>0.6074735110475075</v>
       </c>
-      <c r="H23" t="n">
+      <c r="J23" t="n">
         <v>0.3925135112501448</v>
       </c>
-      <c r="I23" t="n">
+      <c r="K23" t="n">
         <v>1.290575821694673e-05</v>
       </c>
-      <c r="J23" t="n">
+      <c r="L23" t="n">
         <v>0.0003133538067673</v>
       </c>
-      <c r="K23" t="n">
+      <c r="M23" t="n">
         <v>0.9973578015648836</v>
       </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
         <v>1.573836354460511e-05</v>
       </c>
-      <c r="N23" t="n">
+      <c r="P23" t="n">
         <v>4.489709123421717e-08</v>
       </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
         <v>4.087981175031944e-08</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="S23" t="n">
         <v>0.0023124675223448</v>
       </c>
-      <c r="R23" t="n">
+      <c r="T23" t="n">
         <v>2.402441951646609e-07</v>
       </c>
-      <c r="S23" t="n">
+      <c r="U23" t="n">
         <v>2.407772307816696e-07</v>
       </c>
-      <c r="T23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1</v>
-      </c>
       <c r="V23" t="n">
         <v>0</v>
       </c>
@@ -3718,7 +3849,7 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z23" t="n">
         <v>0</v>
@@ -3727,13 +3858,13 @@
         <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>
@@ -3745,7 +3876,7 @@
         <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3754,25 +3885,25 @@
         <v>1</v>
       </c>
       <c r="AK23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR23" t="n">
         <v>0</v>
@@ -3781,78 +3912,84 @@
         <v>0</v>
       </c>
       <c r="AT23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV23" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="inlineStr">
+      <c r="A24" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="n">
+        <v>22</v>
+      </c>
+      <c r="C24" t="inlineStr">
         <is>
           <t>res50_cifar10_layer3.0.conv3</t>
         </is>
       </c>
-      <c r="B24" t="n">
+      <c r="D24" t="n">
         <v>256</v>
       </c>
-      <c r="C24" t="n">
+      <c r="E24" t="n">
         <v>1024</v>
       </c>
-      <c r="D24" t="n">
+      <c r="F24" t="n">
         <v>8</v>
       </c>
-      <c r="E24" t="n">
-        <v>1</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
       <c r="G24" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
         <v>0.9970695128877189</v>
       </c>
-      <c r="H24" t="n">
+      <c r="J24" t="n">
         <v>0.0029172279509224</v>
       </c>
-      <c r="I24" t="n">
+      <c r="K24" t="n">
         <v>1.318721722789544e-05</v>
       </c>
-      <c r="J24" t="n">
+      <c r="L24" t="n">
         <v>0.3107657370665476</v>
       </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
       <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
         <v>0.0137826400945601</v>
       </c>
-      <c r="N24" t="n">
+      <c r="P24" t="n">
         <v>4.131501119688981e-06</v>
       </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
         <v>0.5193382262611816</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="S24" t="n">
         <v>0.1509447336166756</v>
       </c>
-      <c r="R24" t="n">
+      <c r="T24" t="n">
         <v>7.684893760993781e-06</v>
       </c>
-      <c r="S24" t="n">
+      <c r="U24" t="n">
         <v>0.0051554928599768</v>
       </c>
-      <c r="T24" t="n">
+      <c r="V24" t="n">
         <v>1.281762046655575e-06</v>
       </c>
-      <c r="U24" t="n">
-        <v>1</v>
-      </c>
-      <c r="V24" t="n">
-        <v>0</v>
-      </c>
       <c r="W24" t="n">
         <v>1</v>
       </c>
@@ -3860,7 +3997,7 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z24" t="n">
         <v>0</v>
@@ -3869,13 +4006,13 @@
         <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
@@ -3887,7 +4024,7 @@
         <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3896,25 +4033,25 @@
         <v>1</v>
       </c>
       <c r="AK24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR24" t="n">
         <v>0</v>
@@ -3923,78 +4060,84 @@
         <v>0</v>
       </c>
       <c r="AT24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV24" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="inlineStr">
+      <c r="A25" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="n">
+        <v>23</v>
+      </c>
+      <c r="C25" t="inlineStr">
         <is>
           <t>res50_cifar10_layer4.1.conv3</t>
         </is>
       </c>
-      <c r="B25" t="n">
+      <c r="D25" t="n">
         <v>512</v>
       </c>
-      <c r="C25" t="n">
+      <c r="E25" t="n">
         <v>2048</v>
       </c>
-      <c r="D25" t="n">
+      <c r="F25" t="n">
         <v>4</v>
       </c>
-      <c r="E25" t="n">
-        <v>1</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0</v>
-      </c>
       <c r="G25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
         <v>0.9977361899898384</v>
       </c>
-      <c r="H25" t="n">
+      <c r="J25" t="n">
         <v>0.002251180065048</v>
       </c>
-      <c r="I25" t="n">
+      <c r="K25" t="n">
         <v>1.255800098287789e-05</v>
       </c>
-      <c r="J25" t="n">
+      <c r="L25" t="n">
         <v>0.1062440873159112</v>
       </c>
-      <c r="K25" t="n">
+      <c r="M25" t="n">
         <v>0.0023756960582401</v>
       </c>
-      <c r="L25" t="n">
+      <c r="N25" t="n">
         <v>4.304991311373036e-07</v>
       </c>
-      <c r="M25" t="n">
+      <c r="O25" t="n">
         <v>0.0137609430386699</v>
       </c>
-      <c r="N25" t="n">
+      <c r="P25" t="n">
         <v>8.006479490374539e-06</v>
       </c>
-      <c r="O25" t="n">
+      <c r="Q25" t="n">
         <v>3.1933426193899e-10</v>
       </c>
-      <c r="P25" t="n">
+      <c r="R25" t="n">
         <v>0.7243130269401369</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="S25" t="n">
         <v>0.1508994414231808</v>
       </c>
-      <c r="R25" t="n">
+      <c r="T25" t="n">
         <v>0.0005261679082028</v>
       </c>
-      <c r="S25" t="n">
+      <c r="U25" t="n">
         <v>0.0011015730214214</v>
       </c>
-      <c r="T25" t="n">
+      <c r="V25" t="n">
         <v>0.0007705550521501</v>
       </c>
-      <c r="U25" t="n">
-        <v>1</v>
-      </c>
-      <c r="V25" t="n">
-        <v>0</v>
-      </c>
       <c r="W25" t="n">
         <v>1</v>
       </c>
@@ -4002,7 +4145,7 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z25" t="n">
         <v>0</v>
@@ -4011,16 +4154,16 @@
         <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF25" t="n">
         <v>0</v>
@@ -4029,7 +4172,7 @@
         <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -4038,25 +4181,25 @@
         <v>1</v>
       </c>
       <c r="AK25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR25" t="n">
         <v>0</v>
@@ -4065,78 +4208,84 @@
         <v>0</v>
       </c>
       <c r="AT25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV25" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="inlineStr">
+      <c r="A26" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="n">
+        <v>24</v>
+      </c>
+      <c r="C26" t="inlineStr">
         <is>
           <t>vgg11_cifar10_features.11</t>
         </is>
       </c>
-      <c r="B26" t="n">
+      <c r="D26" t="n">
         <v>256</v>
       </c>
-      <c r="C26" t="n">
+      <c r="E26" t="n">
         <v>512</v>
       </c>
-      <c r="D26" t="n">
+      <c r="F26" t="n">
         <v>16</v>
       </c>
-      <c r="E26" t="n">
+      <c r="G26" t="n">
         <v>3</v>
       </c>
-      <c r="F26" t="n">
-        <v>1</v>
-      </c>
-      <c r="G26" t="n">
+      <c r="H26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" t="n">
         <v>0.9978996468957716</v>
       </c>
-      <c r="H26" t="n">
+      <c r="J26" t="n">
         <v>0.002088054393033</v>
       </c>
-      <c r="I26" t="n">
+      <c r="K26" t="n">
         <v>1.222676706468325e-05</v>
       </c>
-      <c r="J26" t="n">
+      <c r="L26" t="n">
         <v>0.2974600457580698</v>
       </c>
-      <c r="K26" t="n">
+      <c r="M26" t="n">
         <v>0.001624688072151</v>
       </c>
-      <c r="L26" t="n">
+      <c r="N26" t="n">
         <v>0.0247956953708013</v>
       </c>
-      <c r="M26" t="n">
+      <c r="O26" t="n">
         <v>0.0075155530605075</v>
       </c>
-      <c r="N26" t="n">
+      <c r="P26" t="n">
         <v>0.0613029286267413</v>
       </c>
-      <c r="O26" t="n">
+      <c r="Q26" t="n">
         <v>0.0612954103802613</v>
       </c>
-      <c r="P26" t="n">
+      <c r="R26" t="n">
         <v>0.5404976629843032</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="S26" t="n">
         <v>2.178973390692558e-05</v>
       </c>
-      <c r="R26" t="n">
+      <c r="T26" t="n">
         <v>0.0010176546260766</v>
       </c>
-      <c r="S26" t="n">
+      <c r="U26" t="n">
         <v>0.0009141519427194</v>
       </c>
-      <c r="T26" t="n">
+      <c r="V26" t="n">
         <v>0.0035543475003304</v>
       </c>
-      <c r="U26" t="n">
-        <v>1</v>
-      </c>
-      <c r="V26" t="n">
-        <v>0</v>
-      </c>
       <c r="W26" t="n">
         <v>1</v>
       </c>
@@ -4144,10 +4293,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -4156,22 +4305,22 @@
         <v>1</v>
       </c>
       <c r="AC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE26" t="n">
         <v>0.99891291148384</v>
       </c>
-      <c r="AD26" t="n">
+      <c r="AF26" t="n">
         <v>0.00108708851616</v>
       </c>
-      <c r="AE26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>0</v>
-      </c>
       <c r="AG26" t="n">
         <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -4180,105 +4329,111 @@
         <v>1</v>
       </c>
       <c r="AK26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR26" t="n">
         <v>0</v>
       </c>
       <c r="AS26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU26" t="n">
         <v>0.1123071720730748</v>
       </c>
-      <c r="AT26" t="n">
+      <c r="AV26" t="n">
         <v>0.8876928279269252</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="inlineStr">
+      <c r="A27" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="n">
+        <v>25</v>
+      </c>
+      <c r="C27" t="inlineStr">
         <is>
           <t>vgg11_cifar10_features.3</t>
         </is>
       </c>
-      <c r="B27" t="n">
+      <c r="D27" t="n">
         <v>64</v>
       </c>
-      <c r="C27" t="n">
+      <c r="E27" t="n">
         <v>128</v>
       </c>
-      <c r="D27" t="n">
+      <c r="F27" t="n">
         <v>4</v>
       </c>
-      <c r="E27" t="n">
+      <c r="G27" t="n">
         <v>3</v>
       </c>
-      <c r="F27" t="n">
-        <v>1</v>
-      </c>
-      <c r="G27" t="n">
+      <c r="H27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" t="n">
         <v>0.9939681638803052</v>
       </c>
-      <c r="H27" t="n">
+      <c r="J27" t="n">
         <v>0.0060208876976284</v>
       </c>
-      <c r="I27" t="n">
+      <c r="K27" t="n">
         <v>1.087647793571727e-05</v>
       </c>
-      <c r="J27" t="n">
+      <c r="L27" t="n">
         <v>0.8111874862260695</v>
       </c>
-      <c r="K27" t="n">
+      <c r="M27" t="n">
         <v>0.0295781053661147</v>
       </c>
-      <c r="L27" t="n">
+      <c r="N27" t="n">
         <v>0.1035142231161751</v>
       </c>
-      <c r="M27" t="n">
+      <c r="O27" t="n">
         <v>0.008146524112237799</v>
       </c>
-      <c r="N27" t="n">
+      <c r="P27" t="n">
         <v>0.0122861472723396</v>
       </c>
-      <c r="O27" t="n">
+      <c r="Q27" t="n">
         <v>0.0280707935795911</v>
       </c>
-      <c r="P27" t="n">
+      <c r="R27" t="n">
         <v>4.531691195160563e-06</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="S27" t="n">
         <v>0.0070666480161183</v>
       </c>
-      <c r="R27" t="n">
+      <c r="T27" t="n">
         <v>4.109323183550703e-06</v>
       </c>
-      <c r="S27" t="n">
+      <c r="U27" t="n">
         <v>8.999504765916507e-06</v>
       </c>
-      <c r="T27" t="n">
+      <c r="V27" t="n">
         <v>0.0001323598480781</v>
       </c>
-      <c r="U27" t="n">
-        <v>1</v>
-      </c>
-      <c r="V27" t="n">
-        <v>0</v>
-      </c>
       <c r="W27" t="n">
         <v>1</v>
       </c>
@@ -4286,10 +4441,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -4298,22 +4453,22 @@
         <v>1</v>
       </c>
       <c r="AC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE27" t="n">
         <v>0.9985468078339056</v>
       </c>
-      <c r="AD27" t="n">
+      <c r="AF27" t="n">
         <v>0.0014531921660943</v>
       </c>
-      <c r="AE27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>0</v>
-      </c>
       <c r="AG27" t="n">
         <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -4322,105 +4477,111 @@
         <v>1</v>
       </c>
       <c r="AK27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR27" t="n">
         <v>0</v>
       </c>
       <c r="AS27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU27" t="n">
         <v>0.112306893237816</v>
       </c>
-      <c r="AT27" t="n">
+      <c r="AV27" t="n">
         <v>0.887693106762184</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="inlineStr">
+      <c r="A28" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="n">
+        <v>26</v>
+      </c>
+      <c r="C28" t="inlineStr">
         <is>
           <t>vgg11_cifar10_features.6</t>
         </is>
       </c>
-      <c r="B28" t="n">
+      <c r="D28" t="n">
         <v>128</v>
       </c>
-      <c r="C28" t="n">
+      <c r="E28" t="n">
         <v>256</v>
       </c>
-      <c r="D28" t="n">
+      <c r="F28" t="n">
         <v>2</v>
       </c>
-      <c r="E28" t="n">
+      <c r="G28" t="n">
         <v>3</v>
       </c>
-      <c r="F28" t="n">
-        <v>1</v>
-      </c>
-      <c r="G28" t="n">
+      <c r="H28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" t="n">
         <v>0.9973987910946808</v>
       </c>
-      <c r="H28" t="n">
+      <c r="J28" t="n">
         <v>0.0025898513951351</v>
       </c>
-      <c r="I28" t="n">
+      <c r="K28" t="n">
         <v>1.128556605328127e-05</v>
       </c>
-      <c r="J28" t="n">
+      <c r="L28" t="n">
         <v>0.5175300796328922</v>
       </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
         <v>0.08155915692772869</v>
       </c>
-      <c r="M28" t="n">
+      <c r="O28" t="n">
         <v>0.0130967257701053</v>
       </c>
-      <c r="N28" t="n">
+      <c r="P28" t="n">
         <v>0.0244753023315731</v>
       </c>
-      <c r="O28" t="n">
+      <c r="Q28" t="n">
         <v>0.0448569048099401</v>
       </c>
-      <c r="P28" t="n">
+      <c r="R28" t="n">
         <v>0.3131683820759409</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="S28" t="n">
         <v>3.652281179583968e-05</v>
       </c>
-      <c r="R28" t="n">
+      <c r="T28" t="n">
         <v>0.0003417657630426</v>
       </c>
-      <c r="S28" t="n">
+      <c r="U28" t="n">
         <v>0.004253275905432</v>
       </c>
-      <c r="T28" t="n">
+      <c r="V28" t="n">
         <v>0.0006818120274181</v>
       </c>
-      <c r="U28" t="n">
-        <v>1</v>
-      </c>
-      <c r="V28" t="n">
-        <v>0</v>
-      </c>
       <c r="W28" t="n">
         <v>1</v>
       </c>
@@ -4428,10 +4589,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4440,22 +4601,22 @@
         <v>1</v>
       </c>
       <c r="AC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE28" t="n">
         <v>0.9989476799554322</v>
       </c>
-      <c r="AD28" t="n">
+      <c r="AF28" t="n">
         <v>0.0010523200445677</v>
       </c>
-      <c r="AE28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>0</v>
-      </c>
       <c r="AG28" t="n">
         <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4464,25 +4625,25 @@
         <v>1</v>
       </c>
       <c r="AK28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR28" t="n">
         <v>0</v>
@@ -4491,78 +4652,84 @@
         <v>0</v>
       </c>
       <c r="AT28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV28" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="inlineStr">
+      <c r="A29" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="n">
+        <v>27</v>
+      </c>
+      <c r="C29" t="inlineStr">
         <is>
           <t>vgg11_cifar10_features.8</t>
         </is>
       </c>
-      <c r="B29" t="n">
+      <c r="D29" t="n">
         <v>256</v>
       </c>
-      <c r="C29" t="n">
+      <c r="E29" t="n">
         <v>256</v>
       </c>
-      <c r="D29" t="n">
+      <c r="F29" t="n">
         <v>2</v>
       </c>
-      <c r="E29" t="n">
+      <c r="G29" t="n">
         <v>3</v>
       </c>
-      <c r="F29" t="n">
-        <v>1</v>
-      </c>
-      <c r="G29" t="n">
+      <c r="H29" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" t="n">
         <v>0.9939839894714136</v>
       </c>
-      <c r="H29" t="n">
+      <c r="J29" t="n">
         <v>0.006004606648117</v>
       </c>
-      <c r="I29" t="n">
+      <c r="K29" t="n">
         <v>1.133193633875389e-05</v>
       </c>
-      <c r="J29" t="n">
+      <c r="L29" t="n">
         <v>0.2440916410489265</v>
       </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
         <v>0.0857285761575015</v>
       </c>
-      <c r="M29" t="n">
+      <c r="O29" t="n">
         <v>0.0146388420997294</v>
       </c>
-      <c r="N29" t="n">
+      <c r="P29" t="n">
         <v>0.0428684782096844</v>
       </c>
-      <c r="O29" t="n">
+      <c r="Q29" t="n">
         <v>0.0171460320715026</v>
       </c>
-      <c r="P29" t="n">
+      <c r="R29" t="n">
         <v>0.588547127851041</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="S29" t="n">
         <v>0.0017351460934031</v>
       </c>
-      <c r="R29" t="n">
+      <c r="T29" t="n">
         <v>0.0010005061817478</v>
       </c>
-      <c r="S29" t="n">
+      <c r="U29" t="n">
         <v>0.0015055738854897</v>
       </c>
-      <c r="T29" t="n">
+      <c r="V29" t="n">
         <v>0.0027379788624883</v>
       </c>
-      <c r="U29" t="n">
-        <v>1</v>
-      </c>
-      <c r="V29" t="n">
-        <v>0</v>
-      </c>
       <c r="W29" t="n">
         <v>1</v>
       </c>
@@ -4570,10 +4737,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4582,22 +4749,22 @@
         <v>1</v>
       </c>
       <c r="AC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE29" t="n">
         <v>0.1123121919592639</v>
       </c>
-      <c r="AD29" t="n">
+      <c r="AF29" t="n">
         <v>0.8876878080407361</v>
       </c>
-      <c r="AE29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>0</v>
-      </c>
       <c r="AG29" t="n">
         <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4606,102 +4773,108 @@
         <v>1</v>
       </c>
       <c r="AK29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR29" t="n">
         <v>0</v>
       </c>
       <c r="AS29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU29" t="n">
         <v>0.0015428068801426</v>
       </c>
-      <c r="AT29" t="n">
+      <c r="AV29" t="n">
         <v>0.9984571931198574</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="inlineStr">
+      <c r="A30" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="n">
+        <v>28</v>
+      </c>
+      <c r="C30" t="inlineStr">
         <is>
           <t>deeplabv3_oxfordpet_backbone.layer2.0.conv1</t>
         </is>
       </c>
-      <c r="B30" t="n">
+      <c r="D30" t="n">
         <v>256</v>
       </c>
-      <c r="C30" t="n">
+      <c r="E30" t="n">
         <v>128</v>
       </c>
-      <c r="D30" t="n">
+      <c r="F30" t="n">
         <v>32</v>
       </c>
-      <c r="E30" t="n">
-        <v>1</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0</v>
-      </c>
       <c r="G30" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
         <v>0.6039185723050603</v>
       </c>
-      <c r="H30" t="n">
+      <c r="J30" t="n">
         <v>0.3960686523785934</v>
       </c>
-      <c r="I30" t="n">
+      <c r="K30" t="n">
         <v>1.270337221528492e-05</v>
       </c>
-      <c r="J30" t="n">
+      <c r="L30" t="n">
         <v>0.0024219406271633</v>
       </c>
-      <c r="K30" t="n">
+      <c r="M30" t="n">
         <v>0.99209511867861</v>
       </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
         <v>1.219955040265368e-06</v>
       </c>
-      <c r="N30" t="n">
+      <c r="P30" t="n">
         <v>6.851568259605964e-08</v>
       </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
         <v>1.824819088788668e-08</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="S30" t="n">
         <v>0.0054815613679229</v>
       </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
         <v>6.63259340144458e-10</v>
       </c>
-      <c r="T30" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
       <c r="V30" t="n">
         <v>0</v>
       </c>
@@ -4721,13 +4894,13 @@
         <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>
@@ -4739,7 +4912,7 @@
         <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4748,22 +4921,22 @@
         <v>1</v>
       </c>
       <c r="AK30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ30" t="n">
         <v>0</v>
@@ -4775,78 +4948,84 @@
         <v>0</v>
       </c>
       <c r="AT30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV30" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="inlineStr">
+      <c r="A31" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="n">
+        <v>29</v>
+      </c>
+      <c r="C31" t="inlineStr">
         <is>
           <t>deeplabv3_oxfordpet_backbone.layer2.3.conv3</t>
         </is>
       </c>
-      <c r="B31" t="n">
+      <c r="D31" t="n">
         <v>128</v>
       </c>
-      <c r="C31" t="n">
+      <c r="E31" t="n">
         <v>512</v>
       </c>
-      <c r="D31" t="n">
+      <c r="F31" t="n">
         <v>16</v>
       </c>
-      <c r="E31" t="n">
-        <v>1</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0</v>
-      </c>
       <c r="G31" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
         <v>0.9942372319630149</v>
       </c>
-      <c r="H31" t="n">
+      <c r="J31" t="n">
         <v>0.0057490723242243</v>
       </c>
-      <c r="I31" t="n">
+      <c r="K31" t="n">
         <v>1.362376862989176e-05</v>
       </c>
-      <c r="J31" t="n">
+      <c r="L31" t="n">
         <v>0.2913398649250131</v>
       </c>
-      <c r="K31" t="n">
+      <c r="M31" t="n">
         <v>0.1845339298320646</v>
       </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="n">
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
         <v>0.0086456688445111</v>
       </c>
-      <c r="N31" t="n">
+      <c r="P31" t="n">
         <v>9.254930074403834e-06</v>
       </c>
-      <c r="O31" t="n">
+      <c r="Q31" t="n">
         <v>0.4066993251370034</v>
       </c>
-      <c r="P31" t="n">
+      <c r="R31" t="n">
         <v>4.750464348188707e-06</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="S31" t="n">
         <v>0.1087555818306137</v>
       </c>
-      <c r="R31" t="n">
+      <c r="T31" t="n">
         <v>3.563595722397861e-06</v>
       </c>
-      <c r="S31" t="n">
+      <c r="U31" t="n">
         <v>8.228413643540755e-07</v>
       </c>
-      <c r="T31" t="n">
+      <c r="V31" t="n">
         <v>7.165655153882498e-06</v>
       </c>
-      <c r="U31" t="n">
-        <v>1</v>
-      </c>
-      <c r="V31" t="n">
-        <v>0</v>
-      </c>
       <c r="W31" t="n">
         <v>1</v>
       </c>
@@ -4854,7 +5033,7 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z31" t="n">
         <v>0</v>
@@ -4863,16 +5042,16 @@
         <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF31" t="n">
         <v>0</v>
@@ -4881,7 +5060,7 @@
         <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4890,25 +5069,25 @@
         <v>1</v>
       </c>
       <c r="AK31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR31" t="n">
         <v>0</v>
@@ -4917,78 +5096,84 @@
         <v>0</v>
       </c>
       <c r="AT31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV31" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="inlineStr">
+      <c r="A32" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" t="n">
+        <v>30</v>
+      </c>
+      <c r="C32" t="inlineStr">
         <is>
           <t>deeplabv3_oxfordpet_backbone.layer3.0.conv3</t>
         </is>
       </c>
-      <c r="B32" t="n">
+      <c r="D32" t="n">
         <v>256</v>
       </c>
-      <c r="C32" t="n">
+      <c r="E32" t="n">
         <v>1024</v>
       </c>
-      <c r="D32" t="n">
+      <c r="F32" t="n">
         <v>16</v>
       </c>
-      <c r="E32" t="n">
-        <v>1</v>
-      </c>
-      <c r="F32" t="n">
-        <v>0</v>
-      </c>
       <c r="G32" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
         <v>0.9878337608721716</v>
       </c>
-      <c r="H32" t="n">
+      <c r="J32" t="n">
         <v>0.0121534044896834</v>
       </c>
-      <c r="I32" t="n">
+      <c r="K32" t="n">
         <v>1.276269401423186e-05</v>
       </c>
-      <c r="J32" t="n">
+      <c r="L32" t="n">
         <v>0.196607632267833</v>
       </c>
-      <c r="K32" t="n">
+      <c r="M32" t="n">
         <v>0.6571424697252665</v>
       </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="n">
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
         <v>0.005860723072928</v>
       </c>
-      <c r="N32" t="n">
+      <c r="P32" t="n">
         <v>7.199600275114015e-06</v>
       </c>
-      <c r="O32" t="n">
+      <c r="Q32" t="n">
         <v>2.862300600227678e-06</v>
       </c>
-      <c r="P32" t="n">
+      <c r="R32" t="n">
         <v>5.267452742536179e-06</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="S32" t="n">
         <v>0.1403606181919595</v>
       </c>
-      <c r="R32" t="n">
+      <c r="T32" t="n">
         <v>4.62940492020306e-06</v>
       </c>
-      <c r="S32" t="n">
+      <c r="U32" t="n">
         <v>5.029526681706946e-06</v>
       </c>
-      <c r="T32" t="n">
+      <c r="V32" t="n">
         <v>3.496512662296734e-06</v>
       </c>
-      <c r="U32" t="n">
-        <v>1</v>
-      </c>
-      <c r="V32" t="n">
-        <v>0</v>
-      </c>
       <c r="W32" t="n">
         <v>1</v>
       </c>
@@ -4996,7 +5181,7 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z32" t="n">
         <v>0</v>
@@ -5005,13 +5190,13 @@
         <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE32" t="n">
         <v>0</v>
@@ -5023,7 +5208,7 @@
         <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -5032,25 +5217,25 @@
         <v>1</v>
       </c>
       <c r="AK32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR32" t="n">
         <v>0</v>
@@ -5059,78 +5244,84 @@
         <v>0</v>
       </c>
       <c r="AT32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV32" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="inlineStr">
+      <c r="A33" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" t="n">
+        <v>31</v>
+      </c>
+      <c r="C33" t="inlineStr">
         <is>
           <t>deeplabv3_oxfordpet_backbone.layer3.1.conv2</t>
         </is>
       </c>
-      <c r="B33" t="n">
+      <c r="D33" t="n">
         <v>256</v>
       </c>
-      <c r="C33" t="n">
+      <c r="E33" t="n">
         <v>256</v>
       </c>
-      <c r="D33" t="n">
+      <c r="F33" t="n">
         <v>16</v>
       </c>
-      <c r="E33" t="n">
+      <c r="G33" t="n">
         <v>3</v>
       </c>
-      <c r="F33" t="n">
+      <c r="H33" t="n">
         <v>2</v>
       </c>
-      <c r="G33" t="n">
+      <c r="I33" t="n">
         <v>0.9822800990318052</v>
       </c>
-      <c r="H33" t="n">
+      <c r="J33" t="n">
         <v>0.0177102005067201</v>
       </c>
-      <c r="I33" t="n">
+      <c r="K33" t="n">
         <v>9.628517343854861e-06</v>
       </c>
-      <c r="J33" t="n">
+      <c r="L33" t="n">
         <v>0.4582112183472372</v>
       </c>
-      <c r="K33" t="n">
+      <c r="M33" t="n">
         <v>0.3947493695276814</v>
       </c>
-      <c r="L33" t="n">
+      <c r="N33" t="n">
         <v>1.063446783806854e-06</v>
       </c>
-      <c r="M33" t="n">
+      <c r="O33" t="n">
         <v>0.0098368440514854</v>
       </c>
-      <c r="N33" t="n">
+      <c r="P33" t="n">
         <v>0.0201240488671294</v>
       </c>
-      <c r="O33" t="n">
+      <c r="Q33" t="n">
         <v>0.1056226469441631</v>
       </c>
-      <c r="P33" t="n">
+      <c r="R33" t="n">
         <v>6.420278713218691e-06</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="S33" t="n">
         <v>3.201751512541992e-05</v>
       </c>
-      <c r="R33" t="n">
+      <c r="T33" t="n">
         <v>0.0001262918735894</v>
       </c>
-      <c r="S33" t="n">
+      <c r="U33" t="n">
         <v>0.0001252551998057</v>
       </c>
-      <c r="T33" t="n">
+      <c r="V33" t="n">
         <v>0.0111646141471378</v>
       </c>
-      <c r="U33" t="n">
-        <v>1</v>
-      </c>
-      <c r="V33" t="n">
-        <v>0</v>
-      </c>
       <c r="W33" t="n">
         <v>1</v>
       </c>
@@ -5138,10 +5329,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -5150,22 +5341,22 @@
         <v>1</v>
       </c>
       <c r="AC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE33" t="n">
         <v>0.1111111111111111</v>
       </c>
-      <c r="AD33" t="n">
+      <c r="AF33" t="n">
         <v>0.8888888888888888</v>
       </c>
-      <c r="AE33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>0</v>
-      </c>
       <c r="AG33" t="n">
         <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -5174,107 +5365,113 @@
         <v>1</v>
       </c>
       <c r="AK33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR33" t="n">
         <v>0</v>
       </c>
       <c r="AS33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU33" t="n">
         <v>0.9992452019200718</v>
       </c>
-      <c r="AT33" t="n">
+      <c r="AV33" t="n">
         <v>0.000754798079928</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="inlineStr">
+      <c r="A34" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" t="n">
+        <v>32</v>
+      </c>
+      <c r="C34" t="inlineStr">
         <is>
           <t>deeplabv3_oxfordpet_backbone.layer4.0.conv2</t>
         </is>
       </c>
-      <c r="B34" t="n">
+      <c r="D34" t="n">
         <v>512</v>
       </c>
-      <c r="C34" t="n">
+      <c r="E34" t="n">
         <v>512</v>
       </c>
-      <c r="D34" t="n">
+      <c r="F34" t="n">
         <v>16</v>
       </c>
-      <c r="E34" t="n">
+      <c r="G34" t="n">
         <v>3</v>
       </c>
-      <c r="F34" t="n">
+      <c r="H34" t="n">
         <v>2</v>
       </c>
-      <c r="G34" t="n">
+      <c r="I34" t="n">
         <v>0.4281463068562242</v>
       </c>
-      <c r="H34" t="n">
+      <c r="J34" t="n">
         <v>0.5718432752913393</v>
       </c>
-      <c r="I34" t="n">
+      <c r="K34" t="n">
         <v>1.03459083057856e-05</v>
       </c>
-      <c r="J34" t="n">
+      <c r="L34" t="n">
         <v>6.095147806080043e-05</v>
       </c>
-      <c r="K34" t="n">
+      <c r="M34" t="n">
         <v>0.9987534056398784</v>
       </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" t="n">
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
         <v>9.169960139188996e-05</v>
       </c>
-      <c r="N34" t="n">
+      <c r="P34" t="n">
         <v>6.711818479000543e-07</v>
       </c>
-      <c r="O34" t="n">
+      <c r="Q34" t="n">
         <v>0.0010460703957919</v>
       </c>
-      <c r="P34" t="n">
+      <c r="R34" t="n">
         <v>1.77500922156731e-07</v>
       </c>
-      <c r="Q34" t="n">
+      <c r="S34" t="n">
         <v>1.957429480255969e-06</v>
       </c>
-      <c r="R34" t="n">
+      <c r="T34" t="n">
         <v>2.234066373980046e-05</v>
       </c>
-      <c r="S34" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" t="n">
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
         <v>2.263592373948528e-05</v>
       </c>
-      <c r="U34" t="n">
-        <v>1</v>
-      </c>
-      <c r="V34" t="n">
-        <v>0</v>
-      </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X34" t="n">
         <v>0</v>
@@ -5283,7 +5480,7 @@
         <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -5292,13 +5489,13 @@
         <v>1</v>
       </c>
       <c r="AC34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF34" t="n">
         <v>0</v>
@@ -5307,7 +5504,7 @@
         <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -5316,25 +5513,25 @@
         <v>1</v>
       </c>
       <c r="AK34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR34" t="n">
         <v>0</v>
@@ -5343,78 +5540,84 @@
         <v>0</v>
       </c>
       <c r="AT34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV34" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="inlineStr">
+      <c r="A35" s="1" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" t="n">
+        <v>33</v>
+      </c>
+      <c r="C35" t="inlineStr">
         <is>
           <t>merge0</t>
         </is>
       </c>
-      <c r="B35" t="n">
+      <c r="D35" t="n">
         <v>3</v>
       </c>
-      <c r="C35" t="n">
+      <c r="E35" t="n">
         <v>64</v>
       </c>
-      <c r="D35" t="n">
+      <c r="F35" t="n">
         <v>32</v>
       </c>
-      <c r="E35" t="n">
+      <c r="G35" t="n">
         <v>3</v>
       </c>
-      <c r="F35" t="n">
-        <v>1</v>
-      </c>
-      <c r="G35" t="n">
+      <c r="H35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" t="n">
         <v>0.9861063583764418</v>
       </c>
-      <c r="H35" t="n">
+      <c r="J35" t="n">
         <v>0.013882674435053</v>
       </c>
-      <c r="I35" t="n">
+      <c r="K35" t="n">
         <v>1.089524437443442e-05</v>
       </c>
-      <c r="J35" t="n">
+      <c r="L35" t="n">
         <v>0.8300987708800671</v>
       </c>
-      <c r="K35" t="n">
+      <c r="M35" t="n">
         <v>0.02235706073385465</v>
       </c>
-      <c r="L35" t="n">
+      <c r="N35" t="n">
         <v>0.0602303899173387</v>
       </c>
-      <c r="M35" t="n">
+      <c r="O35" t="n">
         <v>1.217440698494487e-05</v>
       </c>
-      <c r="N35" t="n">
+      <c r="P35" t="n">
         <v>0.07330529368175046</v>
       </c>
-      <c r="O35" t="n">
+      <c r="Q35" t="n">
         <v>0.004715117609582199</v>
       </c>
-      <c r="P35" t="n">
+      <c r="R35" t="n">
         <v>2.744732319660838e-06</v>
       </c>
-      <c r="Q35" t="n">
+      <c r="S35" t="n">
         <v>0.009275269285480401</v>
       </c>
-      <c r="R35" t="n">
+      <c r="T35" t="n">
         <v>2.991740291103315e-07</v>
       </c>
-      <c r="S35" t="n">
+      <c r="U35" t="n">
         <v>1.72694023547253e-06</v>
       </c>
-      <c r="T35" t="n">
+      <c r="V35" t="n">
         <v>1.08069422628317e-06</v>
       </c>
-      <c r="U35" t="n">
-        <v>1</v>
-      </c>
-      <c r="V35" t="n">
-        <v>0</v>
-      </c>
       <c r="W35" t="n">
         <v>1</v>
       </c>
@@ -5422,7 +5625,7 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z35" t="n">
         <v>0</v>
@@ -5431,7 +5634,7 @@
         <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -5443,13 +5646,13 @@
         <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG35" t="n">
         <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -5458,123 +5661,129 @@
         <v>1</v>
       </c>
       <c r="AK35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR35" t="n">
         <v>0</v>
       </c>
       <c r="AS35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU35" t="n">
         <v>0.1123069957607013</v>
       </c>
-      <c r="AT35" t="n">
+      <c r="AV35" t="n">
         <v>0.8876930042392988</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="inlineStr">
+      <c r="A36" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" t="n">
+        <v>34</v>
+      </c>
+      <c r="C36" t="inlineStr">
         <is>
           <t>merge1</t>
         </is>
       </c>
-      <c r="B36" t="n">
+      <c r="D36" t="n">
         <v>64</v>
       </c>
-      <c r="C36" t="n">
+      <c r="E36" t="n">
         <v>64</v>
       </c>
-      <c r="D36" t="n">
+      <c r="F36" t="n">
         <v>32</v>
       </c>
-      <c r="E36" t="n">
+      <c r="G36" t="n">
         <v>3</v>
       </c>
-      <c r="F36" t="n">
-        <v>1</v>
-      </c>
-      <c r="G36" t="n">
+      <c r="H36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" t="n">
         <v>0.9730003788124798</v>
       </c>
-      <c r="H36" t="n">
+      <c r="J36" t="n">
         <v>0.0269890022343282</v>
       </c>
-      <c r="I36" t="n">
+      <c r="K36" t="n">
         <v>1.054700906135771e-05</v>
       </c>
-      <c r="J36" t="n">
+      <c r="L36" t="n">
         <v>0.7870533063295524</v>
       </c>
-      <c r="K36" t="n">
+      <c r="M36" t="n">
         <v>0.0532798036284725</v>
       </c>
-      <c r="L36" t="n">
+      <c r="N36" t="n">
         <v>0.1068255015687971</v>
       </c>
-      <c r="M36" t="n">
+      <c r="O36" t="n">
         <v>0.008690722778992601</v>
       </c>
-      <c r="N36" t="n">
+      <c r="P36" t="n">
         <v>0.03433123898760725</v>
       </c>
-      <c r="O36" t="n">
+      <c r="Q36" t="n">
         <v>0.0060470306715085</v>
       </c>
-      <c r="P36" t="n">
+      <c r="R36" t="n">
         <v>3.030236078007218e-06</v>
       </c>
-      <c r="Q36" t="n">
+      <c r="S36" t="n">
         <v>0.0035738520932044</v>
       </c>
-      <c r="R36" t="n">
+      <c r="T36" t="n">
         <v>2.19995301185186e-06</v>
       </c>
-      <c r="S36" t="n">
+      <c r="U36" t="n">
         <v>2.066757730556903e-06</v>
       </c>
-      <c r="T36" t="n">
+      <c r="V36" t="n">
         <v>0.0001911750509136396</v>
       </c>
-      <c r="U36" t="n">
+      <c r="W36" t="n">
         <v>0.5</v>
       </c>
-      <c r="V36" t="n">
-        <v>0</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1</v>
-      </c>
       <c r="X36" t="n">
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB36" t="n">
         <v>0.5</v>
       </c>
-      <c r="AA36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1</v>
-      </c>
       <c r="AC36" t="n">
         <v>0</v>
       </c>
@@ -5585,13 +5794,13 @@
         <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5600,105 +5809,111 @@
         <v>1</v>
       </c>
       <c r="AK36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR36" t="n">
         <v>0</v>
       </c>
       <c r="AS36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU36" t="n">
         <v>0.0015410214832947</v>
       </c>
-      <c r="AT36" t="n">
+      <c r="AV36" t="n">
         <v>0.9984589785167053</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="inlineStr">
+      <c r="A37" s="1" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" t="n">
+        <v>35</v>
+      </c>
+      <c r="C37" t="inlineStr">
         <is>
           <t>merge2</t>
         </is>
       </c>
-      <c r="B37" t="n">
+      <c r="D37" t="n">
         <v>128</v>
       </c>
-      <c r="C37" t="n">
+      <c r="E37" t="n">
         <v>128</v>
       </c>
-      <c r="D37" t="n">
+      <c r="F37" t="n">
         <v>16</v>
       </c>
-      <c r="E37" t="n">
+      <c r="G37" t="n">
         <v>3</v>
       </c>
-      <c r="F37" t="n">
-        <v>1</v>
-      </c>
-      <c r="G37" t="n">
+      <c r="H37" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" t="n">
         <v>0.9899345357179963</v>
       </c>
-      <c r="H37" t="n">
+      <c r="J37" t="n">
         <v>0.0100540139827661</v>
       </c>
-      <c r="I37" t="n">
+      <c r="K37" t="n">
         <v>1.137835510691081e-05</v>
       </c>
-      <c r="J37" t="n">
+      <c r="L37" t="n">
         <v>0.4836089060462826</v>
       </c>
-      <c r="K37" t="n">
+      <c r="M37" t="n">
         <v>0.3493454177095232</v>
       </c>
-      <c r="L37" t="n">
+      <c r="N37" t="n">
         <v>0.09281867012800649</v>
       </c>
-      <c r="M37" t="n">
+      <c r="O37" t="n">
         <v>0.0160879502493939</v>
       </c>
-      <c r="N37" t="n">
+      <c r="P37" t="n">
         <v>0.03518628541801435</v>
       </c>
-      <c r="O37" t="n">
+      <c r="Q37" t="n">
         <v>0.01674358794766445</v>
       </c>
-      <c r="P37" t="n">
+      <c r="R37" t="n">
         <v>4.163753369989348e-06</v>
       </c>
-      <c r="Q37" t="n">
+      <c r="S37" t="n">
         <v>0.00537691914951625</v>
       </c>
-      <c r="R37" t="n">
+      <c r="T37" t="n">
         <v>3.546402214983631e-06</v>
       </c>
-      <c r="S37" t="n">
+      <c r="U37" t="n">
         <v>3.15660986737281e-06</v>
       </c>
-      <c r="T37" t="n">
+      <c r="V37" t="n">
         <v>0.0008213246420152983</v>
       </c>
-      <c r="U37" t="n">
-        <v>1</v>
-      </c>
-      <c r="V37" t="n">
-        <v>0</v>
-      </c>
       <c r="W37" t="n">
         <v>1</v>
       </c>
@@ -5706,7 +5921,7 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z37" t="n">
         <v>0</v>
@@ -5715,7 +5930,7 @@
         <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -5727,13 +5942,13 @@
         <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG37" t="n">
         <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5742,25 +5957,25 @@
         <v>1</v>
       </c>
       <c r="AK37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR37" t="n">
         <v>0</v>
@@ -5769,78 +5984,84 @@
         <v>0</v>
       </c>
       <c r="AT37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV37" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="inlineStr">
+      <c r="A38" s="1" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" t="n">
+        <v>36</v>
+      </c>
+      <c r="C38" t="inlineStr">
         <is>
           <t>merge3</t>
         </is>
       </c>
-      <c r="B38" t="n">
+      <c r="D38" t="n">
         <v>256</v>
       </c>
-      <c r="C38" t="n">
+      <c r="E38" t="n">
         <v>256</v>
       </c>
-      <c r="D38" t="n">
+      <c r="F38" t="n">
         <v>8</v>
       </c>
-      <c r="E38" t="n">
+      <c r="G38" t="n">
         <v>3</v>
       </c>
-      <c r="F38" t="n">
-        <v>1</v>
-      </c>
-      <c r="G38" t="n">
+      <c r="H38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" t="n">
         <v>0.9920292527745151</v>
       </c>
-      <c r="H38" t="n">
+      <c r="J38" t="n">
         <v>0.007958957899431849</v>
       </c>
-      <c r="I38" t="n">
+      <c r="K38" t="n">
         <v>1.171738192218124e-05</v>
       </c>
-      <c r="J38" t="n">
+      <c r="L38" t="n">
         <v>0.1321941105946546</v>
       </c>
-      <c r="K38" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" t="n">
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
         <v>0.07821215461237445</v>
       </c>
-      <c r="M38" t="n">
+      <c r="O38" t="n">
         <v>0.0166707717339195</v>
       </c>
-      <c r="N38" t="n">
+      <c r="P38" t="n">
         <v>0.05687424166673165</v>
       </c>
-      <c r="O38" t="n">
+      <c r="Q38" t="n">
         <v>0.006286717972548478</v>
       </c>
-      <c r="P38" t="n">
+      <c r="R38" t="n">
         <v>0.7019180515856612</v>
       </c>
-      <c r="Q38" t="n">
+      <c r="S38" t="n">
         <v>0.0008248291479197852</v>
       </c>
-      <c r="R38" t="n">
+      <c r="T38" t="n">
         <v>0.0001302810139210888</v>
       </c>
-      <c r="S38" t="n">
+      <c r="U38" t="n">
         <v>0.0019519870437844</v>
       </c>
-      <c r="T38" t="n">
+      <c r="V38" t="n">
         <v>0.004936782684353699</v>
       </c>
-      <c r="U38" t="n">
-        <v>1</v>
-      </c>
-      <c r="V38" t="n">
-        <v>0</v>
-      </c>
       <c r="W38" t="n">
         <v>1</v>
       </c>
@@ -5848,34 +6069,34 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB38" t="n">
         <v>0.5</v>
       </c>
-      <c r="AA38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1</v>
-      </c>
       <c r="AC38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE38" t="n">
         <v>0.1111022108638113</v>
       </c>
-      <c r="AD38" t="n">
+      <c r="AF38" t="n">
         <v>0.8888977891361887</v>
       </c>
-      <c r="AE38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>0</v>
-      </c>
       <c r="AG38" t="n">
         <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5884,25 +6105,25 @@
         <v>1</v>
       </c>
       <c r="AK38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM38" t="n">
         <v>0.5</v>
       </c>
-      <c r="AL38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM38" t="n">
-        <v>0</v>
-      </c>
       <c r="AN38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR38" t="n">
         <v>0</v>
@@ -5911,231 +6132,243 @@
         <v>0</v>
       </c>
       <c r="AT38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV38" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="inlineStr">
+      <c r="A39" s="1" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" t="n">
+        <v>37</v>
+      </c>
+      <c r="C39" t="inlineStr">
         <is>
           <t>merge4</t>
         </is>
       </c>
-      <c r="B39" t="n">
+      <c r="D39" t="n">
         <v>512</v>
       </c>
-      <c r="C39" t="n">
+      <c r="E39" t="n">
         <v>512</v>
       </c>
-      <c r="D39" t="n">
+      <c r="F39" t="n">
         <v>4</v>
       </c>
-      <c r="E39" t="n">
+      <c r="G39" t="n">
         <v>3</v>
       </c>
-      <c r="F39" t="n">
-        <v>1</v>
-      </c>
-      <c r="G39" t="n">
+      <c r="H39" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" t="n">
         <v>0.9940755102562981</v>
       </c>
-      <c r="H39" t="n">
+      <c r="J39" t="n">
         <v>0.00591252417566685</v>
       </c>
-      <c r="I39" t="n">
+      <c r="K39" t="n">
         <v>1.189362390425967e-05</v>
       </c>
-      <c r="J39" t="n">
+      <c r="L39" t="n">
         <v>0.05497090428404448</v>
       </c>
-      <c r="K39" t="n">
+      <c r="M39" t="n">
         <v>0.1944860871389585</v>
       </c>
-      <c r="L39" t="n">
+      <c r="N39" t="n">
         <v>0.0338524142028556</v>
       </c>
-      <c r="M39" t="n">
+      <c r="O39" t="n">
         <v>0.007522344082963525</v>
       </c>
-      <c r="N39" t="n">
+      <c r="P39" t="n">
         <v>0.04793809318639938</v>
       </c>
-      <c r="O39" t="n">
+      <c r="Q39" t="n">
         <v>0.0425596085900067</v>
       </c>
-      <c r="P39" t="n">
+      <c r="R39" t="n">
         <v>0.6138753037553797</v>
       </c>
-      <c r="Q39" t="n">
+      <c r="S39" t="n">
         <v>1.588610259149604e-05</v>
       </c>
-      <c r="R39" t="n">
+      <c r="T39" t="n">
         <v>0.002133708736021575</v>
       </c>
-      <c r="S39" t="n">
+      <c r="U39" t="n">
         <v>0.000140162043115538</v>
       </c>
-      <c r="T39" t="n">
+      <c r="V39" t="n">
         <v>0.002505415933532575</v>
       </c>
-      <c r="U39" t="n">
-        <v>1</v>
-      </c>
-      <c r="V39" t="n">
-        <v>0</v>
-      </c>
       <c r="W39" t="n">
+        <v>1</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" t="n">
         <v>0.5</v>
       </c>
-      <c r="X39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>0</v>
-      </c>
       <c r="Z39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB39" t="n">
         <v>0.25</v>
       </c>
-      <c r="AA39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1</v>
-      </c>
       <c r="AC39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE39" t="n">
         <v>0.7492764727841064</v>
       </c>
-      <c r="AD39" t="n">
+      <c r="AF39" t="n">
         <v>0.000723527215893525</v>
       </c>
-      <c r="AE39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>0</v>
-      </c>
       <c r="AG39" t="n">
         <v>0</v>
       </c>
       <c r="AH39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ39" t="n">
         <v>0.75</v>
       </c>
-      <c r="AI39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>1</v>
-      </c>
       <c r="AK39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR39" t="n">
         <v>0</v>
       </c>
       <c r="AS39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU39" t="n">
         <v>0.08423303439649957</v>
       </c>
-      <c r="AT39" t="n">
+      <c r="AV39" t="n">
         <v>0.6657669656035005</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="inlineStr">
+      <c r="A40" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" t="n">
+        <v>38</v>
+      </c>
+      <c r="C40" t="inlineStr">
         <is>
           <t>merge5</t>
         </is>
       </c>
-      <c r="B40" t="n">
+      <c r="D40" t="n">
         <v>512</v>
       </c>
-      <c r="C40" t="n">
+      <c r="E40" t="n">
         <v>512</v>
       </c>
-      <c r="D40" t="n">
+      <c r="F40" t="n">
         <v>8</v>
       </c>
-      <c r="E40" t="n">
+      <c r="G40" t="n">
         <v>3</v>
       </c>
-      <c r="F40" t="n">
-        <v>1</v>
-      </c>
-      <c r="G40" t="n">
+      <c r="H40" t="n">
+        <v>1</v>
+      </c>
+      <c r="I40" t="n">
         <v>0.9978428920126018</v>
       </c>
-      <c r="H40" t="n">
+      <c r="J40" t="n">
         <v>0.00214524925338305</v>
       </c>
-      <c r="I40" t="n">
+      <c r="K40" t="n">
         <v>1.17867898844188e-05</v>
       </c>
-      <c r="J40" t="n">
+      <c r="L40" t="n">
         <v>0.009468709671313349</v>
       </c>
-      <c r="K40" t="n">
+      <c r="M40" t="n">
         <v>0.425605769290682</v>
       </c>
-      <c r="L40" t="n">
+      <c r="N40" t="n">
         <v>0.02468124928288435</v>
       </c>
-      <c r="M40" t="n">
+      <c r="O40" t="n">
         <v>0.00422523241384185</v>
       </c>
-      <c r="N40" t="n">
+      <c r="P40" t="n">
         <v>0.04779108960987315</v>
       </c>
-      <c r="O40" t="n">
+      <c r="Q40" t="n">
         <v>0.06641729538733596</v>
       </c>
-      <c r="P40" t="n">
+      <c r="R40" t="n">
         <v>0.4150020531767502</v>
       </c>
-      <c r="Q40" t="n">
+      <c r="S40" t="n">
         <v>0.002241331754031618</v>
       </c>
-      <c r="R40" t="n">
+      <c r="T40" t="n">
         <v>0.00258629019188605</v>
       </c>
-      <c r="S40" t="n">
+      <c r="U40" t="n">
         <v>8.047127492885e-05</v>
       </c>
-      <c r="T40" t="n">
+      <c r="V40" t="n">
         <v>0.00190043600234145</v>
       </c>
-      <c r="U40" t="n">
-        <v>1</v>
-      </c>
-      <c r="V40" t="n">
-        <v>0</v>
-      </c>
       <c r="W40" t="n">
+        <v>1</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y40" t="n">
         <v>0.5</v>
       </c>
-      <c r="X40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>0</v>
-      </c>
       <c r="Z40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -6144,57 +6377,63 @@
         <v>1</v>
       </c>
       <c r="AC40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE40" t="n">
         <v>0.4990940622388914</v>
       </c>
-      <c r="AD40" t="n">
+      <c r="AF40" t="n">
         <v>0.0009059377611086</v>
       </c>
-      <c r="AE40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>0</v>
-      </c>
       <c r="AG40" t="n">
         <v>0</v>
       </c>
       <c r="AH40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ40" t="n">
         <v>0.5</v>
       </c>
-      <c r="AI40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>1</v>
-      </c>
       <c r="AK40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR40" t="n">
         <v>0</v>
       </c>
       <c r="AS40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU40" t="n">
         <v>0.0561535942356975</v>
       </c>
-      <c r="AT40" t="n">
+      <c r="AV40" t="n">
         <v>0.4438464057643025</v>
       </c>
     </row>
